--- a/Excel/Vertical/hasil_gabungan_semua_sheet.xlsx
+++ b/Excel/Vertical/hasil_gabungan_semua_sheet.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="19">
   <si>
     <t>Kombinasi</t>
   </si>
@@ -49,7 +49,16 @@
     <t>A*</t>
   </si>
   <si>
-    <t>JPS-GL-BRC-PPO</t>
+    <t>BRC</t>
+  </si>
+  <si>
+    <t>GL</t>
+  </si>
+  <si>
+    <t>JPS</t>
+  </si>
+  <si>
+    <t>PPO</t>
   </si>
   <si>
     <t>Map_1</t>
@@ -419,7 +428,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J41"/>
+  <dimension ref="A1:J101"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
@@ -462,7 +471,7 @@
         <v>16</v>
       </c>
       <c r="C2">
-        <v>0.0004396000000000001</v>
+        <v>0.0004530000000000001</v>
       </c>
       <c r="D2" t="s">
         <v>3</v>
@@ -494,284 +503,284 @@
         <v>16</v>
       </c>
       <c r="C3">
-        <v>0.0003564</v>
+        <v>0.0003911</v>
       </c>
       <c r="D3" t="s">
         <v>3</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="F3">
-        <v>23.47851092925225</v>
+        <v>24.97056274847714</v>
       </c>
       <c r="G3">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="H3">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J3">
-        <v>26</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B4">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="C4">
-        <v>0.0033719</v>
+        <v>0.0003456</v>
       </c>
       <c r="D4" t="s">
         <v>3</v>
       </c>
       <c r="E4">
+        <v>21</v>
+      </c>
+      <c r="F4">
+        <v>24.14213562373095</v>
+      </c>
+      <c r="G4">
         <v>42</v>
       </c>
-      <c r="F4">
-        <v>49.698484809835</v>
-      </c>
-      <c r="G4">
-        <v>76</v>
-      </c>
       <c r="H4">
-        <v>241</v>
+        <v>35</v>
       </c>
       <c r="I4">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J4">
-        <v>317</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B5">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="C5">
-        <v>0.0009503</v>
+        <v>0.0003186</v>
       </c>
       <c r="D5" t="s">
         <v>3</v>
       </c>
       <c r="E5">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="F5">
-        <v>48.67111123675181</v>
+        <v>24.14213562373095</v>
       </c>
       <c r="G5">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H5">
         <v>25</v>
       </c>
       <c r="I5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J5">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B6">
-        <v>64</v>
+        <v>16</v>
       </c>
       <c r="C6">
-        <v>0.0238073</v>
+        <v>0.0005079</v>
       </c>
       <c r="D6" t="s">
         <v>3</v>
       </c>
       <c r="E6">
-        <v>84</v>
+        <v>7</v>
       </c>
       <c r="F6">
-        <v>100.8111831820431</v>
+        <v>23.00389691313216</v>
       </c>
       <c r="G6">
-        <v>166</v>
+        <v>30</v>
       </c>
       <c r="H6">
-        <v>983</v>
+        <v>58</v>
       </c>
       <c r="I6">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="J6">
-        <v>1149</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B7">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="C7">
-        <v>0.0029309</v>
+        <v>0.0032506</v>
       </c>
       <c r="D7" t="s">
         <v>3</v>
       </c>
       <c r="E7">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="F7">
-        <v>98.69177760110119</v>
+        <v>49.698484809835</v>
       </c>
       <c r="G7">
-        <v>14</v>
+        <v>76</v>
       </c>
       <c r="H7">
-        <v>26</v>
+        <v>241</v>
       </c>
       <c r="I7">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J7">
-        <v>40</v>
+        <v>317</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B8">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="C8">
-        <v>0.156436</v>
+        <v>0.0012508</v>
       </c>
       <c r="D8" t="s">
         <v>3</v>
       </c>
       <c r="E8">
-        <v>168</v>
+        <v>42</v>
       </c>
       <c r="F8">
-        <v>203.0365799264593</v>
+        <v>50.52691193458118</v>
       </c>
       <c r="G8">
-        <v>379</v>
+        <v>103</v>
       </c>
       <c r="H8">
-        <v>3979</v>
+        <v>45</v>
       </c>
       <c r="I8">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="J8">
-        <v>4358</v>
+        <v>148</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B9">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="C9">
-        <v>0.0107648</v>
+        <v>0.0017691</v>
       </c>
       <c r="D9" t="s">
         <v>3</v>
       </c>
       <c r="E9">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="F9">
-        <v>198.769822173293</v>
+        <v>49.698484809835</v>
       </c>
       <c r="G9">
+        <v>127</v>
+      </c>
+      <c r="H9">
+        <v>132</v>
+      </c>
+      <c r="I9">
         <v>14</v>
       </c>
-      <c r="H9">
-        <v>25</v>
-      </c>
-      <c r="I9">
-        <v>5</v>
-      </c>
       <c r="J9">
-        <v>39</v>
+        <v>259</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B10">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="C10">
-        <v>0.000488</v>
+        <v>0.0010452</v>
       </c>
       <c r="D10" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E10">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F10">
-        <v>25.55634918610405</v>
+        <v>49.69848480983499</v>
       </c>
       <c r="G10">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="H10">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="I10">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="J10">
-        <v>91</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B11">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="C11">
-        <v>0.0003851</v>
+        <v>0.0034012</v>
       </c>
       <c r="D11" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E11">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F11">
-        <v>25.71936168599622</v>
+        <v>46.99910636312252</v>
       </c>
       <c r="G11">
-        <v>12</v>
+        <v>76</v>
       </c>
       <c r="H11">
-        <v>20</v>
+        <v>241</v>
       </c>
       <c r="I11">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J11">
-        <v>32</v>
+        <v>317</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -779,31 +788,31 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="C12">
-        <v>0.002934</v>
+        <v>0.0238787</v>
       </c>
       <c r="D12" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E12">
-        <v>44</v>
+        <v>84</v>
       </c>
       <c r="F12">
-        <v>51.69848480983499</v>
+        <v>100.8111831820431</v>
       </c>
       <c r="G12">
-        <v>63</v>
+        <v>166</v>
       </c>
       <c r="H12">
-        <v>258</v>
+        <v>983</v>
       </c>
       <c r="I12">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J12">
-        <v>321</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -811,287 +820,287 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="C13">
-        <v>0.0010217</v>
+        <v>0.005478100000000001</v>
       </c>
       <c r="D13" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E13">
-        <v>11</v>
+        <v>84</v>
       </c>
       <c r="F13">
-        <v>52.62700551746683</v>
+        <v>103.2964645562817</v>
       </c>
       <c r="G13">
-        <v>13</v>
+        <v>264</v>
       </c>
       <c r="H13">
-        <v>33</v>
+        <v>142</v>
       </c>
       <c r="I13">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="J13">
-        <v>46</v>
+        <v>406</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B14">
         <v>64</v>
       </c>
       <c r="C14">
-        <v>0.0191111</v>
+        <v>0.0118224</v>
       </c>
       <c r="D14" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E14">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="F14">
-        <v>103.9827560572969</v>
+        <v>100.8111831820431</v>
       </c>
       <c r="G14">
-        <v>160</v>
+        <v>326</v>
       </c>
       <c r="H14">
-        <v>1037</v>
+        <v>515</v>
       </c>
       <c r="I14">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="J14">
-        <v>1197</v>
+        <v>841</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B15">
         <v>64</v>
       </c>
       <c r="C15">
-        <v>0.0027238</v>
+        <v>0.0034616</v>
       </c>
       <c r="D15" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E15">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F15">
-        <v>105.9675221282317</v>
+        <v>100.8111831820431</v>
       </c>
       <c r="G15">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H15">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="I15">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J15">
-        <v>44</v>
+        <v>54</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B16">
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="C16">
-        <v>0.1264418</v>
+        <v>0.0230443</v>
       </c>
       <c r="D16" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E16">
-        <v>176</v>
+        <v>7</v>
       </c>
       <c r="F16">
-        <v>208.5512985522207</v>
+        <v>95.57049943528645</v>
       </c>
       <c r="G16">
-        <v>362</v>
+        <v>166</v>
       </c>
       <c r="H16">
-        <v>4153</v>
+        <v>983</v>
       </c>
       <c r="I16">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="J16">
-        <v>4515</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B17">
         <v>128</v>
       </c>
       <c r="C17">
-        <v>0.0114242</v>
+        <v>0.1490245</v>
       </c>
       <c r="D17" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E17">
-        <v>11</v>
+        <v>168</v>
       </c>
       <c r="F17">
-        <v>212.7549252358647</v>
+        <v>203.0365799264593</v>
       </c>
       <c r="G17">
-        <v>12</v>
+        <v>379</v>
       </c>
       <c r="H17">
-        <v>38</v>
+        <v>3979</v>
       </c>
       <c r="I17">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="J17">
-        <v>50</v>
+        <v>4358</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B18">
-        <v>16</v>
+        <v>128</v>
       </c>
       <c r="C18">
-        <v>0.0003684</v>
+        <v>0.0402807</v>
       </c>
       <c r="D18" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="E18">
-        <v>23</v>
+        <v>168</v>
       </c>
       <c r="F18">
-        <v>25.31370849898476</v>
+        <v>208.0071426749365</v>
       </c>
       <c r="G18">
-        <v>13</v>
+        <v>643</v>
       </c>
       <c r="H18">
-        <v>59</v>
+        <v>587</v>
       </c>
       <c r="I18">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="J18">
-        <v>72</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B19">
-        <v>16</v>
+        <v>128</v>
       </c>
       <c r="C19">
-        <v>0.0003829</v>
+        <v>0.08020040000000001</v>
       </c>
       <c r="D19" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="E19">
-        <v>13</v>
+        <v>168</v>
       </c>
       <c r="F19">
-        <v>24.77927174436484</v>
+        <v>203.0365799264593</v>
       </c>
       <c r="G19">
-        <v>10</v>
+        <v>739</v>
       </c>
       <c r="H19">
-        <v>23</v>
+        <v>2026</v>
       </c>
       <c r="I19">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J19">
-        <v>33</v>
+        <v>2765</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B20">
-        <v>32</v>
+        <v>128</v>
       </c>
       <c r="C20">
-        <v>0.002488</v>
+        <v>0.0140568</v>
       </c>
       <c r="D20" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="E20">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="F20">
-        <v>52.04163056034262</v>
+        <v>203.0365799264593</v>
       </c>
       <c r="G20">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="H20">
-        <v>244</v>
+        <v>41</v>
       </c>
       <c r="I20">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="J20">
-        <v>288</v>
+        <v>59</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B21">
-        <v>32</v>
+        <v>128</v>
       </c>
       <c r="C21">
-        <v>0.0008588000000000001</v>
+        <v>0.1485451</v>
       </c>
       <c r="D21" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="E21">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="F21">
-        <v>53.34219364008838</v>
+        <v>191.4295326143042</v>
       </c>
       <c r="G21">
-        <v>15</v>
+        <v>379</v>
       </c>
       <c r="H21">
-        <v>31</v>
+        <v>3979</v>
       </c>
       <c r="I21">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="J21">
-        <v>46</v>
+        <v>4358</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -1099,31 +1108,31 @@
         <v>10</v>
       </c>
       <c r="B22">
-        <v>64</v>
+        <v>16</v>
       </c>
       <c r="C22">
-        <v>0.0161375</v>
+        <v>0.0004585</v>
       </c>
       <c r="D22" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E22">
-        <v>92</v>
+        <v>22</v>
       </c>
       <c r="F22">
-        <v>105.4974746830583</v>
+        <v>25.55634918610405</v>
       </c>
       <c r="G22">
-        <v>124</v>
+        <v>25</v>
       </c>
       <c r="H22">
-        <v>980</v>
+        <v>66</v>
       </c>
       <c r="I22">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="J22">
-        <v>1104</v>
+        <v>91</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -1131,287 +1140,287 @@
         <v>11</v>
       </c>
       <c r="B23">
-        <v>64</v>
+        <v>16</v>
       </c>
       <c r="C23">
-        <v>0.0027321</v>
+        <v>0.0005399</v>
       </c>
       <c r="D23" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E23">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F23">
-        <v>107.9564652188189</v>
+        <v>28.38477631085023</v>
       </c>
       <c r="G23">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="H23">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I23">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J23">
-        <v>48</v>
+        <v>72</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B24">
-        <v>128</v>
+        <v>16</v>
       </c>
       <c r="C24">
-        <v>0.1062307</v>
+        <v>0.0003932</v>
       </c>
       <c r="D24" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E24">
-        <v>184</v>
+        <v>22</v>
       </c>
       <c r="F24">
-        <v>212.4091629284898</v>
+        <v>25.55634918610405</v>
       </c>
       <c r="G24">
-        <v>266</v>
+        <v>29</v>
       </c>
       <c r="H24">
-        <v>3919</v>
+        <v>51</v>
       </c>
       <c r="I24">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="J24">
-        <v>4185</v>
+        <v>80</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" t="s">
+        <v>13</v>
+      </c>
+      <c r="B25">
+        <v>16</v>
+      </c>
+      <c r="C25">
+        <v>0.0003333</v>
+      </c>
+      <c r="D25" t="s">
+        <v>15</v>
+      </c>
+      <c r="E25">
+        <v>18</v>
+      </c>
+      <c r="F25">
+        <v>25.55634918610405</v>
+      </c>
+      <c r="G25">
+        <v>10</v>
+      </c>
+      <c r="H25">
+        <v>33</v>
+      </c>
+      <c r="I25">
         <v>11</v>
       </c>
-      <c r="B25">
-        <v>128</v>
-      </c>
-      <c r="C25">
-        <v>0.0102487</v>
-      </c>
-      <c r="D25" t="s">
-        <v>13</v>
-      </c>
-      <c r="E25">
-        <v>17</v>
-      </c>
-      <c r="F25">
-        <v>216.4987168752647</v>
-      </c>
-      <c r="G25">
-        <v>16</v>
-      </c>
-      <c r="H25">
-        <v>31</v>
-      </c>
-      <c r="I25">
-        <v>15</v>
-      </c>
       <c r="J25">
-        <v>47</v>
+        <v>43</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B26">
         <v>16</v>
       </c>
       <c r="C26">
-        <v>0.000546</v>
+        <v>0.000512</v>
       </c>
       <c r="D26" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E26">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F26">
-        <v>23.55634918610405</v>
+        <v>24.41488446708389</v>
       </c>
       <c r="G26">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="H26">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="I26">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J26">
-        <v>104</v>
+        <v>91</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B27">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="C27">
-        <v>0.0003426999999999999</v>
+        <v>0.0028168</v>
       </c>
       <c r="D27" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E27">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="F27">
-        <v>22.93245190266634</v>
+        <v>51.69848480983499</v>
       </c>
       <c r="G27">
-        <v>12</v>
+        <v>63</v>
       </c>
       <c r="H27">
-        <v>17</v>
+        <v>258</v>
       </c>
       <c r="I27">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J27">
-        <v>29</v>
+        <v>321</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B28">
         <v>32</v>
       </c>
       <c r="C28">
-        <v>0.003684000000000001</v>
+        <v>0.0018485</v>
       </c>
       <c r="D28" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E28">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F28">
-        <v>48.52691193458118</v>
+        <v>52.52691193458119</v>
       </c>
       <c r="G28">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="H28">
-        <v>276</v>
+        <v>77</v>
       </c>
       <c r="I28">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J28">
-        <v>390</v>
+        <v>182</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B29">
         <v>32</v>
       </c>
       <c r="C29">
-        <v>0.0007721000000000001</v>
+        <v>0.0023093</v>
       </c>
       <c r="D29" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E29">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="F29">
-        <v>47.27911736770578</v>
+        <v>51.69848480983499</v>
       </c>
       <c r="G29">
-        <v>17</v>
+        <v>107</v>
       </c>
       <c r="H29">
-        <v>26</v>
+        <v>200</v>
       </c>
       <c r="I29">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J29">
-        <v>43</v>
+        <v>307</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B30">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="C30">
-        <v>0.030357</v>
+        <v>0.0009808</v>
       </c>
       <c r="D30" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E30">
-        <v>80</v>
+        <v>19</v>
       </c>
       <c r="F30">
-        <v>98.46803743153546</v>
+        <v>51.69848480983499</v>
       </c>
       <c r="G30">
-        <v>352</v>
+        <v>13</v>
       </c>
       <c r="H30">
-        <v>1159</v>
+        <v>43</v>
       </c>
       <c r="I30">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="J30">
-        <v>1511</v>
+        <v>56</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B31">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="C31">
-        <v>0.0022251</v>
+        <v>0.0029314</v>
       </c>
       <c r="D31" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E31">
         <v>8</v>
       </c>
       <c r="F31">
-        <v>95.97244829778465</v>
+        <v>49.03946295574199</v>
       </c>
       <c r="G31">
-        <v>17</v>
+        <v>63</v>
       </c>
       <c r="H31">
-        <v>25</v>
+        <v>258</v>
       </c>
       <c r="I31">
         <v>6</v>
       </c>
       <c r="J31">
-        <v>42</v>
+        <v>321</v>
       </c>
     </row>
     <row r="32" spans="1:10">
@@ -1419,31 +1428,31 @@
         <v>10</v>
       </c>
       <c r="B32">
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="C32">
-        <v>0.2180022</v>
+        <v>0.0190411</v>
       </c>
       <c r="D32" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E32">
+        <v>88</v>
+      </c>
+      <c r="F32">
+        <v>103.9827560572969</v>
+      </c>
+      <c r="G32">
         <v>160</v>
       </c>
-      <c r="F32">
-        <v>198.350288425444</v>
-      </c>
-      <c r="G32">
-        <v>873</v>
-      </c>
       <c r="H32">
-        <v>4844</v>
+        <v>1037</v>
       </c>
       <c r="I32">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="J32">
-        <v>5717</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="33" spans="1:10">
@@ -1451,287 +1460,2207 @@
         <v>11</v>
       </c>
       <c r="B33">
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="C33">
-        <v>0.007606700000000001</v>
+        <v>0.0163242</v>
       </c>
       <c r="D33" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E33">
-        <v>8</v>
+        <v>88</v>
       </c>
       <c r="F33">
-        <v>193.3591101579424</v>
+        <v>107.2964645562817</v>
       </c>
       <c r="G33">
-        <v>17</v>
+        <v>331</v>
       </c>
       <c r="H33">
-        <v>25</v>
+        <v>395</v>
       </c>
       <c r="I33">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="J33">
-        <v>42</v>
+        <v>726</v>
       </c>
     </row>
     <row r="34" spans="1:10">
       <c r="A34" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B34">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="C34">
-        <v>0.0007156</v>
+        <v>0.0154216</v>
       </c>
       <c r="D34" t="s">
         <v>15</v>
       </c>
       <c r="E34">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="F34">
-        <v>22.97056274847714</v>
+        <v>103.9827560572969</v>
       </c>
       <c r="G34">
-        <v>73</v>
+        <v>260</v>
       </c>
       <c r="H34">
-        <v>77</v>
+        <v>758</v>
       </c>
       <c r="I34">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J34">
-        <v>150</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="35" spans="1:10">
       <c r="A35" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B35">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="C35">
-        <v>0.0003775</v>
+        <v>0.003392399999999999</v>
       </c>
       <c r="D35" t="s">
         <v>15</v>
       </c>
       <c r="E35">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="F35">
-        <v>22.84376684661083</v>
+        <v>103.9827560572969</v>
       </c>
       <c r="G35">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="H35">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="I35">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="J35">
-        <v>20</v>
+        <v>57</v>
       </c>
     </row>
     <row r="36" spans="1:10">
       <c r="A36" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B36">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="C36">
-        <v>0.0055638</v>
+        <v>0.0183713</v>
       </c>
       <c r="D36" t="s">
         <v>15</v>
       </c>
       <c r="E36">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="F36">
-        <v>47.35533905932738</v>
+        <v>99.30085278599736</v>
       </c>
       <c r="G36">
-        <v>252</v>
+        <v>160</v>
       </c>
       <c r="H36">
-        <v>296</v>
+        <v>1037</v>
       </c>
       <c r="I36">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="J36">
-        <v>548</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="37" spans="1:10">
       <c r="A37" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B37">
-        <v>32</v>
+        <v>128</v>
       </c>
       <c r="C37">
-        <v>0.0011277</v>
+        <v>0.121997</v>
       </c>
       <c r="D37" t="s">
         <v>15</v>
       </c>
       <c r="E37">
-        <v>5</v>
+        <v>176</v>
       </c>
       <c r="F37">
-        <v>46.69946093319749</v>
+        <v>208.5512985522207</v>
       </c>
       <c r="G37">
-        <v>9</v>
+        <v>362</v>
       </c>
       <c r="H37">
-        <v>16</v>
+        <v>4153</v>
       </c>
       <c r="I37">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="J37">
-        <v>25</v>
+        <v>4515</v>
       </c>
     </row>
     <row r="38" spans="1:10">
       <c r="A38" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B38">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="C38">
-        <v>0.0476005</v>
+        <v>0.1526633</v>
       </c>
       <c r="D38" t="s">
         <v>15</v>
       </c>
       <c r="E38">
-        <v>76</v>
+        <v>176</v>
       </c>
       <c r="F38">
-        <v>96.12489168102785</v>
+        <v>214.350288425444</v>
       </c>
       <c r="G38">
-        <v>578</v>
+        <v>836</v>
       </c>
       <c r="H38">
-        <v>1204</v>
+        <v>1847</v>
       </c>
       <c r="I38">
         <v>24</v>
       </c>
       <c r="J38">
-        <v>1782</v>
+        <v>2683</v>
       </c>
     </row>
     <row r="39" spans="1:10">
       <c r="A39" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B39">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="C39">
-        <v>0.0037401</v>
+        <v>0.1059115</v>
       </c>
       <c r="D39" t="s">
         <v>15</v>
       </c>
       <c r="E39">
-        <v>5</v>
+        <v>176</v>
       </c>
       <c r="F39">
-        <v>94.48572750867693</v>
+        <v>208.5512985522207</v>
       </c>
       <c r="G39">
-        <v>9</v>
+        <v>554</v>
       </c>
       <c r="H39">
-        <v>16</v>
+        <v>2986</v>
       </c>
       <c r="I39">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="J39">
-        <v>25</v>
+        <v>3540</v>
       </c>
     </row>
     <row r="40" spans="1:10">
       <c r="A40" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B40">
         <v>128</v>
       </c>
       <c r="C40">
-        <v>0.3275252</v>
+        <v>0.0122929</v>
       </c>
       <c r="D40" t="s">
         <v>15</v>
       </c>
       <c r="E40">
-        <v>152</v>
+        <v>19</v>
       </c>
       <c r="F40">
-        <v>193.6639969244288</v>
+        <v>208.5512985522207</v>
       </c>
       <c r="G40">
-        <v>1281</v>
+        <v>14</v>
       </c>
       <c r="H40">
-        <v>4902</v>
+        <v>43</v>
       </c>
       <c r="I40">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="J40">
-        <v>6183</v>
+        <v>57</v>
       </c>
     </row>
     <row r="41" spans="1:10">
       <c r="A41" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B41">
         <v>128</v>
       </c>
       <c r="C41">
-        <v>0.0138309</v>
+        <v>0.1215531</v>
       </c>
       <c r="D41" t="s">
         <v>15</v>
       </c>
       <c r="E41">
+        <v>8</v>
+      </c>
+      <c r="F41">
+        <v>198.924964802366</v>
+      </c>
+      <c r="G41">
+        <v>362</v>
+      </c>
+      <c r="H41">
+        <v>4153</v>
+      </c>
+      <c r="I41">
+        <v>6</v>
+      </c>
+      <c r="J41">
+        <v>4515</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10">
+      <c r="A42" t="s">
+        <v>10</v>
+      </c>
+      <c r="B42">
+        <v>16</v>
+      </c>
+      <c r="C42">
+        <v>0.0003786</v>
+      </c>
+      <c r="D42" t="s">
+        <v>16</v>
+      </c>
+      <c r="E42">
+        <v>23</v>
+      </c>
+      <c r="F42">
+        <v>25.31370849898476</v>
+      </c>
+      <c r="G42">
+        <v>13</v>
+      </c>
+      <c r="H42">
+        <v>59</v>
+      </c>
+      <c r="I42">
+        <v>11</v>
+      </c>
+      <c r="J42">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10">
+      <c r="A43" t="s">
+        <v>11</v>
+      </c>
+      <c r="B43">
+        <v>16</v>
+      </c>
+      <c r="C43">
+        <v>0.0002895</v>
+      </c>
+      <c r="D43" t="s">
+        <v>16</v>
+      </c>
+      <c r="E43">
+        <v>24</v>
+      </c>
+      <c r="F43">
+        <v>26.72792206135786</v>
+      </c>
+      <c r="G43">
+        <v>19</v>
+      </c>
+      <c r="H43">
+        <v>25</v>
+      </c>
+      <c r="I43">
+        <v>15</v>
+      </c>
+      <c r="J43">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10">
+      <c r="A44" t="s">
+        <v>12</v>
+      </c>
+      <c r="B44">
+        <v>16</v>
+      </c>
+      <c r="C44">
+        <v>0.0003137</v>
+      </c>
+      <c r="D44" t="s">
+        <v>16</v>
+      </c>
+      <c r="E44">
+        <v>23</v>
+      </c>
+      <c r="F44">
+        <v>25.31370849898476</v>
+      </c>
+      <c r="G44">
+        <v>18</v>
+      </c>
+      <c r="H44">
+        <v>47</v>
+      </c>
+      <c r="I44">
+        <v>13</v>
+      </c>
+      <c r="J44">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10">
+      <c r="A45" t="s">
+        <v>13</v>
+      </c>
+      <c r="B45">
+        <v>16</v>
+      </c>
+      <c r="C45">
+        <v>0.0003942</v>
+      </c>
+      <c r="D45" t="s">
+        <v>16</v>
+      </c>
+      <c r="E45">
+        <v>17</v>
+      </c>
+      <c r="F45">
+        <v>25.31370849898476</v>
+      </c>
+      <c r="G45">
+        <v>4</v>
+      </c>
+      <c r="H45">
+        <v>37</v>
+      </c>
+      <c r="I45">
+        <v>11</v>
+      </c>
+      <c r="J45">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10">
+      <c r="A46" t="s">
+        <v>14</v>
+      </c>
+      <c r="B46">
+        <v>16</v>
+      </c>
+      <c r="C46">
+        <v>0.0004014</v>
+      </c>
+      <c r="D46" t="s">
+        <v>16</v>
+      </c>
+      <c r="E46">
+        <v>11</v>
+      </c>
+      <c r="F46">
+        <v>24.55639589508264</v>
+      </c>
+      <c r="G46">
+        <v>13</v>
+      </c>
+      <c r="H46">
+        <v>59</v>
+      </c>
+      <c r="I46">
+        <v>9</v>
+      </c>
+      <c r="J46">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10">
+      <c r="A47" t="s">
+        <v>10</v>
+      </c>
+      <c r="B47">
+        <v>32</v>
+      </c>
+      <c r="C47">
+        <v>0.002459499999999999</v>
+      </c>
+      <c r="D47" t="s">
+        <v>16</v>
+      </c>
+      <c r="E47">
+        <v>46</v>
+      </c>
+      <c r="F47">
+        <v>52.04163056034262</v>
+      </c>
+      <c r="G47">
+        <v>44</v>
+      </c>
+      <c r="H47">
+        <v>244</v>
+      </c>
+      <c r="I47">
+        <v>16</v>
+      </c>
+      <c r="J47">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10">
+      <c r="A48" t="s">
+        <v>11</v>
+      </c>
+      <c r="B48">
+        <v>32</v>
+      </c>
+      <c r="C48">
+        <v>0.0013014</v>
+      </c>
+      <c r="D48" t="s">
+        <v>16</v>
+      </c>
+      <c r="E48">
+        <v>48</v>
+      </c>
+      <c r="F48">
+        <v>54.04163056034262</v>
+      </c>
+      <c r="G48">
+        <v>67</v>
+      </c>
+      <c r="H48">
+        <v>64</v>
+      </c>
+      <c r="I48">
+        <v>16</v>
+      </c>
+      <c r="J48">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10">
+      <c r="A49" t="s">
+        <v>12</v>
+      </c>
+      <c r="B49">
+        <v>32</v>
+      </c>
+      <c r="C49">
+        <v>0.0018837</v>
+      </c>
+      <c r="D49" t="s">
+        <v>16</v>
+      </c>
+      <c r="E49">
+        <v>46</v>
+      </c>
+      <c r="F49">
+        <v>52.04163056034262</v>
+      </c>
+      <c r="G49">
+        <v>55</v>
+      </c>
+      <c r="H49">
+        <v>179</v>
+      </c>
+      <c r="I49">
+        <v>16</v>
+      </c>
+      <c r="J49">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10">
+      <c r="A50" t="s">
+        <v>13</v>
+      </c>
+      <c r="B50">
+        <v>32</v>
+      </c>
+      <c r="C50">
+        <v>0.0012408</v>
+      </c>
+      <c r="D50" t="s">
+        <v>16</v>
+      </c>
+      <c r="E50">
+        <v>24</v>
+      </c>
+      <c r="F50">
+        <v>52.04163056034262</v>
+      </c>
+      <c r="G50">
         <v>5</v>
       </c>
-      <c r="F41">
-        <v>190.0974453381104</v>
-      </c>
-      <c r="G41">
+      <c r="H50">
+        <v>59</v>
+      </c>
+      <c r="I50">
+        <v>14</v>
+      </c>
+      <c r="J50">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10">
+      <c r="A51" t="s">
+        <v>14</v>
+      </c>
+      <c r="B51">
+        <v>32</v>
+      </c>
+      <c r="C51">
+        <v>0.0025718</v>
+      </c>
+      <c r="D51" t="s">
+        <v>16</v>
+      </c>
+      <c r="E51">
+        <v>11</v>
+      </c>
+      <c r="F51">
+        <v>49.99028453499244</v>
+      </c>
+      <c r="G51">
+        <v>44</v>
+      </c>
+      <c r="H51">
+        <v>244</v>
+      </c>
+      <c r="I51">
         <v>9</v>
       </c>
-      <c r="H41">
-        <v>16</v>
-      </c>
-      <c r="I41">
+      <c r="J51">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10">
+      <c r="A52" t="s">
+        <v>10</v>
+      </c>
+      <c r="B52">
+        <v>64</v>
+      </c>
+      <c r="C52">
+        <v>0.015765</v>
+      </c>
+      <c r="D52" t="s">
+        <v>16</v>
+      </c>
+      <c r="E52">
+        <v>92</v>
+      </c>
+      <c r="F52">
+        <v>105.4974746830583</v>
+      </c>
+      <c r="G52">
+        <v>124</v>
+      </c>
+      <c r="H52">
+        <v>980</v>
+      </c>
+      <c r="I52">
+        <v>22</v>
+      </c>
+      <c r="J52">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10">
+      <c r="A53" t="s">
+        <v>11</v>
+      </c>
+      <c r="B53">
+        <v>64</v>
+      </c>
+      <c r="C53">
+        <v>0.008706700000000001</v>
+      </c>
+      <c r="D53" t="s">
+        <v>16</v>
+      </c>
+      <c r="E53">
+        <v>92</v>
+      </c>
+      <c r="F53">
+        <v>106.3259018078045</v>
+      </c>
+      <c r="G53">
+        <v>229</v>
+      </c>
+      <c r="H53">
+        <v>267</v>
+      </c>
+      <c r="I53">
+        <v>26</v>
+      </c>
+      <c r="J53">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10">
+      <c r="A54" t="s">
+        <v>12</v>
+      </c>
+      <c r="B54">
+        <v>64</v>
+      </c>
+      <c r="C54">
+        <v>0.0125769</v>
+      </c>
+      <c r="D54" t="s">
+        <v>16</v>
+      </c>
+      <c r="E54">
+        <v>92</v>
+      </c>
+      <c r="F54">
+        <v>105.4974746830583</v>
+      </c>
+      <c r="G54">
+        <v>122</v>
+      </c>
+      <c r="H54">
+        <v>700</v>
+      </c>
+      <c r="I54">
+        <v>18</v>
+      </c>
+      <c r="J54">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10">
+      <c r="A55" t="s">
+        <v>13</v>
+      </c>
+      <c r="B55">
+        <v>64</v>
+      </c>
+      <c r="C55">
+        <v>0.0046645</v>
+      </c>
+      <c r="D55" t="s">
+        <v>16</v>
+      </c>
+      <c r="E55">
+        <v>22</v>
+      </c>
+      <c r="F55">
+        <v>105.4974746830583</v>
+      </c>
+      <c r="G55">
+        <v>7</v>
+      </c>
+      <c r="H55">
+        <v>60</v>
+      </c>
+      <c r="I55">
+        <v>12</v>
+      </c>
+      <c r="J55">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10">
+      <c r="A56" t="s">
+        <v>14</v>
+      </c>
+      <c r="B56">
+        <v>64</v>
+      </c>
+      <c r="C56">
+        <v>0.0172327</v>
+      </c>
+      <c r="D56" t="s">
+        <v>16</v>
+      </c>
+      <c r="E56">
+        <v>11</v>
+      </c>
+      <c r="F56">
+        <v>100.6498597519346</v>
+      </c>
+      <c r="G56">
+        <v>124</v>
+      </c>
+      <c r="H56">
+        <v>980</v>
+      </c>
+      <c r="I56">
+        <v>9</v>
+      </c>
+      <c r="J56">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10">
+      <c r="A57" t="s">
+        <v>10</v>
+      </c>
+      <c r="B57">
+        <v>128</v>
+      </c>
+      <c r="C57">
+        <v>0.1020895</v>
+      </c>
+      <c r="D57" t="s">
+        <v>16</v>
+      </c>
+      <c r="E57">
+        <v>184</v>
+      </c>
+      <c r="F57">
+        <v>212.4091629284898</v>
+      </c>
+      <c r="G57">
+        <v>266</v>
+      </c>
+      <c r="H57">
+        <v>3919</v>
+      </c>
+      <c r="I57">
+        <v>26</v>
+      </c>
+      <c r="J57">
+        <v>4185</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10">
+      <c r="A58" t="s">
+        <v>11</v>
+      </c>
+      <c r="B58">
+        <v>128</v>
+      </c>
+      <c r="C58">
+        <v>0.0652737</v>
+      </c>
+      <c r="D58" t="s">
+        <v>16</v>
+      </c>
+      <c r="E58">
+        <v>184</v>
+      </c>
+      <c r="F58">
+        <v>214.0660171779821</v>
+      </c>
+      <c r="G58">
+        <v>544</v>
+      </c>
+      <c r="H58">
+        <v>1070</v>
+      </c>
+      <c r="I58">
+        <v>30</v>
+      </c>
+      <c r="J58">
+        <v>1614</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10">
+      <c r="A59" t="s">
+        <v>12</v>
+      </c>
+      <c r="B59">
+        <v>128</v>
+      </c>
+      <c r="C59">
+        <v>0.08295180000000001</v>
+      </c>
+      <c r="D59" t="s">
+        <v>16</v>
+      </c>
+      <c r="E59">
+        <v>184</v>
+      </c>
+      <c r="F59">
+        <v>212.4091629284898</v>
+      </c>
+      <c r="G59">
+        <v>270</v>
+      </c>
+      <c r="H59">
+        <v>2767</v>
+      </c>
+      <c r="I59">
+        <v>18</v>
+      </c>
+      <c r="J59">
+        <v>3037</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10">
+      <c r="A60" t="s">
+        <v>13</v>
+      </c>
+      <c r="B60">
+        <v>128</v>
+      </c>
+      <c r="C60">
+        <v>0.0199562</v>
+      </c>
+      <c r="D60" t="s">
+        <v>16</v>
+      </c>
+      <c r="E60">
+        <v>24</v>
+      </c>
+      <c r="F60">
+        <v>212.4091629284898</v>
+      </c>
+      <c r="G60">
+        <v>10</v>
+      </c>
+      <c r="H60">
+        <v>61</v>
+      </c>
+      <c r="I60">
+        <v>14</v>
+      </c>
+      <c r="J60">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10">
+      <c r="A61" t="s">
+        <v>14</v>
+      </c>
+      <c r="B61">
+        <v>128</v>
+      </c>
+      <c r="C61">
+        <v>0.102782</v>
+      </c>
+      <c r="D61" t="s">
+        <v>16</v>
+      </c>
+      <c r="E61">
+        <v>11</v>
+      </c>
+      <c r="F61">
+        <v>203.2060918012439</v>
+      </c>
+      <c r="G61">
+        <v>266</v>
+      </c>
+      <c r="H61">
+        <v>3919</v>
+      </c>
+      <c r="I61">
+        <v>9</v>
+      </c>
+      <c r="J61">
+        <v>4185</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10">
+      <c r="A62" t="s">
+        <v>10</v>
+      </c>
+      <c r="B62">
+        <v>16</v>
+      </c>
+      <c r="C62">
+        <v>0.0005406</v>
+      </c>
+      <c r="D62" t="s">
+        <v>17</v>
+      </c>
+      <c r="E62">
+        <v>20</v>
+      </c>
+      <c r="F62">
+        <v>23.55634918610405</v>
+      </c>
+      <c r="G62">
+        <v>34</v>
+      </c>
+      <c r="H62">
+        <v>70</v>
+      </c>
+      <c r="I62">
+        <v>10</v>
+      </c>
+      <c r="J62">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10">
+      <c r="A63" t="s">
+        <v>11</v>
+      </c>
+      <c r="B63">
+        <v>16</v>
+      </c>
+      <c r="C63">
+        <v>0.000384</v>
+      </c>
+      <c r="D63" t="s">
+        <v>17</v>
+      </c>
+      <c r="E63">
+        <v>20</v>
+      </c>
+      <c r="F63">
+        <v>24.38477631085024</v>
+      </c>
+      <c r="G63">
+        <v>38</v>
+      </c>
+      <c r="H63">
+        <v>21</v>
+      </c>
+      <c r="I63">
+        <v>9</v>
+      </c>
+      <c r="J63">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10">
+      <c r="A64" t="s">
+        <v>12</v>
+      </c>
+      <c r="B64">
+        <v>16</v>
+      </c>
+      <c r="C64">
+        <v>0.0004287</v>
+      </c>
+      <c r="D64" t="s">
+        <v>17</v>
+      </c>
+      <c r="E64">
+        <v>20</v>
+      </c>
+      <c r="F64">
+        <v>23.55634918610405</v>
+      </c>
+      <c r="G64">
+        <v>39</v>
+      </c>
+      <c r="H64">
+        <v>48</v>
+      </c>
+      <c r="I64">
+        <v>12</v>
+      </c>
+      <c r="J64">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10">
+      <c r="A65" t="s">
+        <v>13</v>
+      </c>
+      <c r="B65">
+        <v>16</v>
+      </c>
+      <c r="C65">
+        <v>0.0004063000000000001</v>
+      </c>
+      <c r="D65" t="s">
+        <v>17</v>
+      </c>
+      <c r="E65">
+        <v>18</v>
+      </c>
+      <c r="F65">
+        <v>23.55634918610405</v>
+      </c>
+      <c r="G65">
+        <v>15</v>
+      </c>
+      <c r="H65">
+        <v>37</v>
+      </c>
+      <c r="I65">
+        <v>9</v>
+      </c>
+      <c r="J65">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10">
+      <c r="A66" t="s">
+        <v>14</v>
+      </c>
+      <c r="B66">
+        <v>16</v>
+      </c>
+      <c r="C66">
+        <v>0.0005910999999999999</v>
+      </c>
+      <c r="D66" t="s">
+        <v>17</v>
+      </c>
+      <c r="E66">
+        <v>7</v>
+      </c>
+      <c r="F66">
+        <v>22.57616073291973</v>
+      </c>
+      <c r="G66">
+        <v>34</v>
+      </c>
+      <c r="H66">
+        <v>70</v>
+      </c>
+      <c r="I66">
+        <v>5</v>
+      </c>
+      <c r="J66">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10">
+      <c r="A67" t="s">
+        <v>10</v>
+      </c>
+      <c r="B67">
+        <v>32</v>
+      </c>
+      <c r="C67">
+        <v>0.0035912</v>
+      </c>
+      <c r="D67" t="s">
+        <v>17</v>
+      </c>
+      <c r="E67">
+        <v>40</v>
+      </c>
+      <c r="F67">
+        <v>48.52691193458118</v>
+      </c>
+      <c r="G67">
+        <v>114</v>
+      </c>
+      <c r="H67">
+        <v>276</v>
+      </c>
+      <c r="I67">
+        <v>14</v>
+      </c>
+      <c r="J67">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10">
+      <c r="A68" t="s">
+        <v>11</v>
+      </c>
+      <c r="B68">
+        <v>32</v>
+      </c>
+      <c r="C68">
+        <v>0.0013739</v>
+      </c>
+      <c r="D68" t="s">
+        <v>17</v>
+      </c>
+      <c r="E68">
+        <v>40</v>
+      </c>
+      <c r="F68">
+        <v>50.18376618407358</v>
+      </c>
+      <c r="G68">
+        <v>91</v>
+      </c>
+      <c r="H68">
+        <v>61</v>
+      </c>
+      <c r="I68">
+        <v>16</v>
+      </c>
+      <c r="J68">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10">
+      <c r="A69" t="s">
+        <v>12</v>
+      </c>
+      <c r="B69">
+        <v>32</v>
+      </c>
+      <c r="C69">
+        <v>0.0025759</v>
+      </c>
+      <c r="D69" t="s">
+        <v>17</v>
+      </c>
+      <c r="E69">
+        <v>40</v>
+      </c>
+      <c r="F69">
+        <v>48.52691193458118</v>
+      </c>
+      <c r="G69">
+        <v>102</v>
+      </c>
+      <c r="H69">
+        <v>185</v>
+      </c>
+      <c r="I69">
+        <v>14</v>
+      </c>
+      <c r="J69">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10">
+      <c r="A70" t="s">
+        <v>13</v>
+      </c>
+      <c r="B70">
+        <v>32</v>
+      </c>
+      <c r="C70">
+        <v>0.0012948</v>
+      </c>
+      <c r="D70" t="s">
+        <v>17</v>
+      </c>
+      <c r="E70">
+        <v>24</v>
+      </c>
+      <c r="F70">
+        <v>48.52691193458118</v>
+      </c>
+      <c r="G70">
+        <v>20</v>
+      </c>
+      <c r="H70">
+        <v>59</v>
+      </c>
+      <c r="I70">
+        <v>13</v>
+      </c>
+      <c r="J70">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10">
+      <c r="A71" t="s">
+        <v>14</v>
+      </c>
+      <c r="B71">
+        <v>32</v>
+      </c>
+      <c r="C71">
+        <v>0.0036794</v>
+      </c>
+      <c r="D71" t="s">
+        <v>17</v>
+      </c>
+      <c r="E71">
+        <v>8</v>
+      </c>
+      <c r="F71">
+        <v>46.54043818792906</v>
+      </c>
+      <c r="G71">
+        <v>114</v>
+      </c>
+      <c r="H71">
+        <v>276</v>
+      </c>
+      <c r="I71">
+        <v>6</v>
+      </c>
+      <c r="J71">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10">
+      <c r="A72" t="s">
+        <v>10</v>
+      </c>
+      <c r="B72">
+        <v>64</v>
+      </c>
+      <c r="C72">
+        <v>0.0287193</v>
+      </c>
+      <c r="D72" t="s">
+        <v>17</v>
+      </c>
+      <c r="E72">
+        <v>80</v>
+      </c>
+      <c r="F72">
+        <v>98.46803743153546</v>
+      </c>
+      <c r="G72">
+        <v>352</v>
+      </c>
+      <c r="H72">
+        <v>1159</v>
+      </c>
+      <c r="I72">
+        <v>20</v>
+      </c>
+      <c r="J72">
+        <v>1511</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10">
+      <c r="A73" t="s">
+        <v>11</v>
+      </c>
+      <c r="B73">
+        <v>64</v>
+      </c>
+      <c r="C73">
+        <v>0.0054597</v>
+      </c>
+      <c r="D73" t="s">
+        <v>17</v>
+      </c>
+      <c r="E73">
+        <v>81</v>
+      </c>
+      <c r="F73">
+        <v>102.3675323681472</v>
+      </c>
+      <c r="G73">
+        <v>230</v>
+      </c>
+      <c r="H73">
+        <v>160</v>
+      </c>
+      <c r="I73">
+        <v>21</v>
+      </c>
+      <c r="J73">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10">
+      <c r="A74" t="s">
+        <v>12</v>
+      </c>
+      <c r="B74">
+        <v>64</v>
+      </c>
+      <c r="C74">
+        <v>0.01683</v>
+      </c>
+      <c r="D74" t="s">
+        <v>17</v>
+      </c>
+      <c r="E74">
+        <v>80</v>
+      </c>
+      <c r="F74">
+        <v>98.46803743153546</v>
+      </c>
+      <c r="G74">
+        <v>240</v>
+      </c>
+      <c r="H74">
+        <v>717</v>
+      </c>
+      <c r="I74">
+        <v>14</v>
+      </c>
+      <c r="J74">
+        <v>957</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10">
+      <c r="A75" t="s">
+        <v>13</v>
+      </c>
+      <c r="B75">
+        <v>64</v>
+      </c>
+      <c r="C75">
+        <v>0.004711600000000001</v>
+      </c>
+      <c r="D75" t="s">
+        <v>17</v>
+      </c>
+      <c r="E75">
+        <v>24</v>
+      </c>
+      <c r="F75">
+        <v>98.46803743153546</v>
+      </c>
+      <c r="G75">
+        <v>25</v>
+      </c>
+      <c r="H75">
+        <v>63</v>
+      </c>
+      <c r="I75">
+        <v>13</v>
+      </c>
+      <c r="J75">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10">
+      <c r="A76" t="s">
+        <v>14</v>
+      </c>
+      <c r="B76">
+        <v>64</v>
+      </c>
+      <c r="C76">
+        <v>0.027812</v>
+      </c>
+      <c r="D76" t="s">
+        <v>17</v>
+      </c>
+      <c r="E76">
+        <v>9</v>
+      </c>
+      <c r="F76">
+        <v>92.90052844970226</v>
+      </c>
+      <c r="G76">
+        <v>352</v>
+      </c>
+      <c r="H76">
+        <v>1159</v>
+      </c>
+      <c r="I76">
+        <v>7</v>
+      </c>
+      <c r="J76">
+        <v>1511</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10">
+      <c r="A77" t="s">
+        <v>10</v>
+      </c>
+      <c r="B77">
+        <v>128</v>
+      </c>
+      <c r="C77">
+        <v>0.208237</v>
+      </c>
+      <c r="D77" t="s">
+        <v>17</v>
+      </c>
+      <c r="E77">
+        <v>160</v>
+      </c>
+      <c r="F77">
+        <v>198.350288425444</v>
+      </c>
+      <c r="G77">
+        <v>873</v>
+      </c>
+      <c r="H77">
+        <v>4844</v>
+      </c>
+      <c r="I77">
+        <v>28</v>
+      </c>
+      <c r="J77">
+        <v>5717</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10">
+      <c r="A78" t="s">
+        <v>11</v>
+      </c>
+      <c r="B78">
+        <v>128</v>
+      </c>
+      <c r="C78">
+        <v>0.0346657</v>
+      </c>
+      <c r="D78" t="s">
+        <v>17</v>
+      </c>
+      <c r="E78">
+        <v>161</v>
+      </c>
+      <c r="F78">
+        <v>204.7350647362943</v>
+      </c>
+      <c r="G78">
+        <v>625</v>
+      </c>
+      <c r="H78">
+        <v>581</v>
+      </c>
+      <c r="I78">
+        <v>29</v>
+      </c>
+      <c r="J78">
+        <v>1206</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10">
+      <c r="A79" t="s">
+        <v>12</v>
+      </c>
+      <c r="B79">
+        <v>128</v>
+      </c>
+      <c r="C79">
+        <v>0.1163257</v>
+      </c>
+      <c r="D79" t="s">
+        <v>17</v>
+      </c>
+      <c r="E79">
+        <v>160</v>
+      </c>
+      <c r="F79">
+        <v>198.350288425444</v>
+      </c>
+      <c r="G79">
+        <v>540</v>
+      </c>
+      <c r="H79">
+        <v>2864</v>
+      </c>
+      <c r="I79">
+        <v>12</v>
+      </c>
+      <c r="J79">
+        <v>3404</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10">
+      <c r="A80" t="s">
+        <v>13</v>
+      </c>
+      <c r="B80">
+        <v>128</v>
+      </c>
+      <c r="C80">
+        <v>0.01906</v>
+      </c>
+      <c r="D80" t="s">
+        <v>17</v>
+      </c>
+      <c r="E80">
+        <v>22</v>
+      </c>
+      <c r="F80">
+        <v>198.350288425444</v>
+      </c>
+      <c r="G80">
+        <v>22</v>
+      </c>
+      <c r="H80">
+        <v>67</v>
+      </c>
+      <c r="I80">
+        <v>9</v>
+      </c>
+      <c r="J80">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10">
+      <c r="A81" t="s">
+        <v>14</v>
+      </c>
+      <c r="B81">
+        <v>128</v>
+      </c>
+      <c r="C81">
+        <v>0.2072281999999999</v>
+      </c>
+      <c r="D81" t="s">
+        <v>17</v>
+      </c>
+      <c r="E81">
+        <v>8</v>
+      </c>
+      <c r="F81">
+        <v>190.4679384542775</v>
+      </c>
+      <c r="G81">
+        <v>873</v>
+      </c>
+      <c r="H81">
+        <v>4844</v>
+      </c>
+      <c r="I81">
+        <v>6</v>
+      </c>
+      <c r="J81">
+        <v>5717</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10">
+      <c r="A82" t="s">
+        <v>10</v>
+      </c>
+      <c r="B82">
+        <v>16</v>
+      </c>
+      <c r="C82">
+        <v>0.000717</v>
+      </c>
+      <c r="D82" t="s">
+        <v>18</v>
+      </c>
+      <c r="E82">
+        <v>19</v>
+      </c>
+      <c r="F82">
+        <v>22.97056274847714</v>
+      </c>
+      <c r="G82">
+        <v>73</v>
+      </c>
+      <c r="H82">
+        <v>77</v>
+      </c>
+      <c r="I82">
+        <v>5</v>
+      </c>
+      <c r="J82">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10">
+      <c r="A83" t="s">
+        <v>11</v>
+      </c>
+      <c r="B83">
+        <v>16</v>
+      </c>
+      <c r="C83">
+        <v>0.0004643000000000001</v>
+      </c>
+      <c r="D83" t="s">
+        <v>18</v>
+      </c>
+      <c r="E83">
+        <v>20</v>
+      </c>
+      <c r="F83">
+        <v>24.38477631085024</v>
+      </c>
+      <c r="G83">
+        <v>42</v>
+      </c>
+      <c r="H83">
+        <v>21</v>
+      </c>
+      <c r="I83">
+        <v>7</v>
+      </c>
+      <c r="J83">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10">
+      <c r="A84" t="s">
+        <v>12</v>
+      </c>
+      <c r="B84">
+        <v>16</v>
+      </c>
+      <c r="C84">
+        <v>0.0006058</v>
+      </c>
+      <c r="D84" t="s">
+        <v>18</v>
+      </c>
+      <c r="E84">
+        <v>19</v>
+      </c>
+      <c r="F84">
+        <v>22.97056274847714</v>
+      </c>
+      <c r="G84">
+        <v>71</v>
+      </c>
+      <c r="H84">
+        <v>53</v>
+      </c>
+      <c r="I84">
         <v>3</v>
       </c>
-      <c r="J41">
+      <c r="J84">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10">
+      <c r="A85" t="s">
+        <v>13</v>
+      </c>
+      <c r="B85">
+        <v>16</v>
+      </c>
+      <c r="C85">
+        <v>0.0005839</v>
+      </c>
+      <c r="D85" t="s">
+        <v>18</v>
+      </c>
+      <c r="E85">
+        <v>10</v>
+      </c>
+      <c r="F85">
+        <v>22.97056274847714</v>
+      </c>
+      <c r="G85">
+        <v>11</v>
+      </c>
+      <c r="H85">
         <v>25</v>
+      </c>
+      <c r="I85">
+        <v>2</v>
+      </c>
+      <c r="J85">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10">
+      <c r="A86" t="s">
+        <v>14</v>
+      </c>
+      <c r="B86">
+        <v>16</v>
+      </c>
+      <c r="C86">
+        <v>0.0008386999999999998</v>
+      </c>
+      <c r="D86" t="s">
+        <v>18</v>
+      </c>
+      <c r="E86">
+        <v>4</v>
+      </c>
+      <c r="F86">
+        <v>22.52730043086546</v>
+      </c>
+      <c r="G86">
+        <v>73</v>
+      </c>
+      <c r="H86">
+        <v>77</v>
+      </c>
+      <c r="I86">
+        <v>2</v>
+      </c>
+      <c r="J86">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10">
+      <c r="A87" t="s">
+        <v>10</v>
+      </c>
+      <c r="B87">
+        <v>32</v>
+      </c>
+      <c r="C87">
+        <v>0.0055118</v>
+      </c>
+      <c r="D87" t="s">
+        <v>18</v>
+      </c>
+      <c r="E87">
+        <v>38</v>
+      </c>
+      <c r="F87">
+        <v>47.35533905932738</v>
+      </c>
+      <c r="G87">
+        <v>252</v>
+      </c>
+      <c r="H87">
+        <v>296</v>
+      </c>
+      <c r="I87">
+        <v>12</v>
+      </c>
+      <c r="J87">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10">
+      <c r="A88" t="s">
+        <v>11</v>
+      </c>
+      <c r="B88">
+        <v>32</v>
+      </c>
+      <c r="C88">
+        <v>0.001511</v>
+      </c>
+      <c r="D88" t="s">
+        <v>18</v>
+      </c>
+      <c r="E88">
+        <v>40</v>
+      </c>
+      <c r="F88">
+        <v>49.35533905932738</v>
+      </c>
+      <c r="G88">
+        <v>104</v>
+      </c>
+      <c r="H88">
+        <v>58</v>
+      </c>
+      <c r="I88">
+        <v>8</v>
+      </c>
+      <c r="J88">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10">
+      <c r="A89" t="s">
+        <v>12</v>
+      </c>
+      <c r="B89">
+        <v>32</v>
+      </c>
+      <c r="C89">
+        <v>0.0034278</v>
+      </c>
+      <c r="D89" t="s">
+        <v>18</v>
+      </c>
+      <c r="E89">
+        <v>38</v>
+      </c>
+      <c r="F89">
+        <v>47.35533905932738</v>
+      </c>
+      <c r="G89">
+        <v>197</v>
+      </c>
+      <c r="H89">
+        <v>191</v>
+      </c>
+      <c r="I89">
+        <v>4</v>
+      </c>
+      <c r="J89">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10">
+      <c r="A90" t="s">
+        <v>13</v>
+      </c>
+      <c r="B90">
+        <v>32</v>
+      </c>
+      <c r="C90">
+        <v>0.0020146</v>
+      </c>
+      <c r="D90" t="s">
+        <v>18</v>
+      </c>
+      <c r="E90">
+        <v>12</v>
+      </c>
+      <c r="F90">
+        <v>47.35533905932738</v>
+      </c>
+      <c r="G90">
+        <v>10</v>
+      </c>
+      <c r="H90">
+        <v>29</v>
+      </c>
+      <c r="I90">
+        <v>3</v>
+      </c>
+      <c r="J90">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10">
+      <c r="A91" t="s">
+        <v>14</v>
+      </c>
+      <c r="B91">
+        <v>32</v>
+      </c>
+      <c r="C91">
+        <v>0.0055471</v>
+      </c>
+      <c r="D91" t="s">
+        <v>18</v>
+      </c>
+      <c r="E91">
+        <v>4</v>
+      </c>
+      <c r="F91">
+        <v>46.02417147054884</v>
+      </c>
+      <c r="G91">
+        <v>252</v>
+      </c>
+      <c r="H91">
+        <v>296</v>
+      </c>
+      <c r="I91">
+        <v>2</v>
+      </c>
+      <c r="J91">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10">
+      <c r="A92" t="s">
+        <v>10</v>
+      </c>
+      <c r="B92">
+        <v>64</v>
+      </c>
+      <c r="C92">
+        <v>0.0465013</v>
+      </c>
+      <c r="D92" t="s">
+        <v>18</v>
+      </c>
+      <c r="E92">
+        <v>76</v>
+      </c>
+      <c r="F92">
+        <v>96.12489168102785</v>
+      </c>
+      <c r="G92">
+        <v>578</v>
+      </c>
+      <c r="H92">
+        <v>1204</v>
+      </c>
+      <c r="I92">
+        <v>24</v>
+      </c>
+      <c r="J92">
+        <v>1782</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10">
+      <c r="A93" t="s">
+        <v>11</v>
+      </c>
+      <c r="B93">
+        <v>64</v>
+      </c>
+      <c r="C93">
+        <v>0.0108756</v>
+      </c>
+      <c r="D93" t="s">
+        <v>18</v>
+      </c>
+      <c r="E93">
+        <v>80</v>
+      </c>
+      <c r="F93">
+        <v>100.1248916810278</v>
+      </c>
+      <c r="G93">
+        <v>292</v>
+      </c>
+      <c r="H93">
+        <v>263</v>
+      </c>
+      <c r="I93">
+        <v>8</v>
+      </c>
+      <c r="J93">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10">
+      <c r="A94" t="s">
+        <v>12</v>
+      </c>
+      <c r="B94">
+        <v>64</v>
+      </c>
+      <c r="C94">
+        <v>0.0223417</v>
+      </c>
+      <c r="D94" t="s">
+        <v>18</v>
+      </c>
+      <c r="E94">
+        <v>76</v>
+      </c>
+      <c r="F94">
+        <v>96.12489168102785</v>
+      </c>
+      <c r="G94">
+        <v>419</v>
+      </c>
+      <c r="H94">
+        <v>710</v>
+      </c>
+      <c r="I94">
+        <v>6</v>
+      </c>
+      <c r="J94">
+        <v>1129</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10">
+      <c r="A95" t="s">
+        <v>13</v>
+      </c>
+      <c r="B95">
+        <v>64</v>
+      </c>
+      <c r="C95">
+        <v>0.007431200000000001</v>
+      </c>
+      <c r="D95" t="s">
+        <v>18</v>
+      </c>
+      <c r="E95">
+        <v>12</v>
+      </c>
+      <c r="F95">
+        <v>96.12489168102785</v>
+      </c>
+      <c r="G95">
+        <v>12</v>
+      </c>
+      <c r="H95">
+        <v>28</v>
+      </c>
+      <c r="I95">
+        <v>3</v>
+      </c>
+      <c r="J95">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10">
+      <c r="A96" t="s">
+        <v>14</v>
+      </c>
+      <c r="B96">
+        <v>64</v>
+      </c>
+      <c r="C96">
+        <v>0.04703710000000001</v>
+      </c>
+      <c r="D96" t="s">
+        <v>18</v>
+      </c>
+      <c r="E96">
+        <v>4</v>
+      </c>
+      <c r="F96">
+        <v>93.2032658581451</v>
+      </c>
+      <c r="G96">
+        <v>578</v>
+      </c>
+      <c r="H96">
+        <v>1204</v>
+      </c>
+      <c r="I96">
+        <v>2</v>
+      </c>
+      <c r="J96">
+        <v>1782</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10">
+      <c r="A97" t="s">
+        <v>10</v>
+      </c>
+      <c r="B97">
+        <v>128</v>
+      </c>
+      <c r="C97">
+        <v>0.3183174</v>
+      </c>
+      <c r="D97" t="s">
+        <v>18</v>
+      </c>
+      <c r="E97">
+        <v>152</v>
+      </c>
+      <c r="F97">
+        <v>193.6639969244288</v>
+      </c>
+      <c r="G97">
+        <v>1281</v>
+      </c>
+      <c r="H97">
+        <v>4902</v>
+      </c>
+      <c r="I97">
+        <v>42</v>
+      </c>
+      <c r="J97">
+        <v>6183</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10">
+      <c r="A98" t="s">
+        <v>11</v>
+      </c>
+      <c r="B98">
+        <v>128</v>
+      </c>
+      <c r="C98">
+        <v>0.092317</v>
+      </c>
+      <c r="D98" t="s">
+        <v>18</v>
+      </c>
+      <c r="E98">
+        <v>161</v>
+      </c>
+      <c r="F98">
+        <v>202.2497833620557</v>
+      </c>
+      <c r="G98">
+        <v>614</v>
+      </c>
+      <c r="H98">
+        <v>1176</v>
+      </c>
+      <c r="I98">
+        <v>10</v>
+      </c>
+      <c r="J98">
+        <v>1790</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10">
+      <c r="A99" t="s">
+        <v>12</v>
+      </c>
+      <c r="B99">
+        <v>128</v>
+      </c>
+      <c r="C99">
+        <v>0.1514367</v>
+      </c>
+      <c r="D99" t="s">
+        <v>18</v>
+      </c>
+      <c r="E99">
+        <v>152</v>
+      </c>
+      <c r="F99">
+        <v>193.6639969244288</v>
+      </c>
+      <c r="G99">
+        <v>790</v>
+      </c>
+      <c r="H99">
+        <v>2816</v>
+      </c>
+      <c r="I99">
+        <v>4</v>
+      </c>
+      <c r="J99">
+        <v>3606</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10">
+      <c r="A100" t="s">
+        <v>13</v>
+      </c>
+      <c r="B100">
+        <v>128</v>
+      </c>
+      <c r="C100">
+        <v>0.030449</v>
+      </c>
+      <c r="D100" t="s">
+        <v>18</v>
+      </c>
+      <c r="E100">
+        <v>12</v>
+      </c>
+      <c r="F100">
+        <v>193.6639969244288</v>
+      </c>
+      <c r="G100">
+        <v>12</v>
+      </c>
+      <c r="H100">
+        <v>29</v>
+      </c>
+      <c r="I100">
+        <v>3</v>
+      </c>
+      <c r="J100">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10">
+      <c r="A101" t="s">
+        <v>14</v>
+      </c>
+      <c r="B101">
+        <v>128</v>
+      </c>
+      <c r="C101">
+        <v>0.3183032</v>
+      </c>
+      <c r="D101" t="s">
+        <v>18</v>
+      </c>
+      <c r="E101">
+        <v>4</v>
+      </c>
+      <c r="F101">
+        <v>187.5929117988749</v>
+      </c>
+      <c r="G101">
+        <v>1281</v>
+      </c>
+      <c r="H101">
+        <v>4902</v>
+      </c>
+      <c r="I101">
+        <v>2</v>
+      </c>
+      <c r="J101">
+        <v>6183</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/Vertical/hasil_gabungan_semua_sheet.xlsx
+++ b/Excel/Vertical/hasil_gabungan_semua_sheet.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="21">
   <si>
     <t>Kombinasi</t>
   </si>
@@ -49,6 +49,9 @@
     <t>A*</t>
   </si>
   <si>
+    <t>BDS</t>
+  </si>
+  <si>
     <t>BRC</t>
   </si>
   <si>
@@ -59,6 +62,9 @@
   </si>
   <si>
     <t>PPO</t>
+  </si>
+  <si>
+    <t>TPF</t>
   </si>
   <si>
     <t>Map_1</t>
@@ -428,7 +434,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J101"/>
+  <dimension ref="A1:J141"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
@@ -471,7 +477,7 @@
         <v>16</v>
       </c>
       <c r="C2">
-        <v>0.0004530000000000001</v>
+        <v>0.0004822</v>
       </c>
       <c r="D2" t="s">
         <v>3</v>
@@ -503,7 +509,7 @@
         <v>16</v>
       </c>
       <c r="C3">
-        <v>0.0003911</v>
+        <v>0.0002534999999999999</v>
       </c>
       <c r="D3" t="s">
         <v>3</v>
@@ -512,19 +518,19 @@
         <v>21</v>
       </c>
       <c r="F3">
-        <v>24.97056274847714</v>
+        <v>24.14213562373095</v>
       </c>
       <c r="G3">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H3">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="I3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J3">
-        <v>60</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -535,7 +541,7 @@
         <v>16</v>
       </c>
       <c r="C4">
-        <v>0.0003456</v>
+        <v>0.0004101</v>
       </c>
       <c r="D4" t="s">
         <v>3</v>
@@ -544,19 +550,19 @@
         <v>21</v>
       </c>
       <c r="F4">
-        <v>24.14213562373095</v>
+        <v>24.97056274847714</v>
       </c>
       <c r="G4">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H4">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I4">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J4">
-        <v>77</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -567,28 +573,28 @@
         <v>16</v>
       </c>
       <c r="C5">
-        <v>0.0003186</v>
+        <v>0.0003179</v>
       </c>
       <c r="D5" t="s">
         <v>3</v>
       </c>
       <c r="E5">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F5">
         <v>24.14213562373095</v>
       </c>
       <c r="G5">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="H5">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="I5">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="J5">
-        <v>37</v>
+        <v>77</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -599,103 +605,103 @@
         <v>16</v>
       </c>
       <c r="C6">
-        <v>0.0005079</v>
+        <v>0.0003319</v>
       </c>
       <c r="D6" t="s">
         <v>3</v>
       </c>
       <c r="E6">
+        <v>16</v>
+      </c>
+      <c r="F6">
+        <v>24.14213562373095</v>
+      </c>
+      <c r="G6">
+        <v>12</v>
+      </c>
+      <c r="H6">
+        <v>25</v>
+      </c>
+      <c r="I6">
         <v>7</v>
       </c>
-      <c r="F6">
-        <v>23.00389691313216</v>
-      </c>
-      <c r="G6">
-        <v>30</v>
-      </c>
-      <c r="H6">
-        <v>58</v>
-      </c>
-      <c r="I6">
-        <v>5</v>
-      </c>
       <c r="J6">
-        <v>88</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="B7">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="C7">
-        <v>0.0032506</v>
+        <v>0.0005113</v>
       </c>
       <c r="D7" t="s">
         <v>3</v>
       </c>
       <c r="E7">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="F7">
-        <v>49.698484809835</v>
+        <v>23.09901951359279</v>
       </c>
       <c r="G7">
-        <v>76</v>
+        <v>30</v>
       </c>
       <c r="H7">
-        <v>241</v>
+        <v>58</v>
       </c>
       <c r="I7">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="J7">
-        <v>317</v>
+        <v>88</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B8">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="C8">
-        <v>0.0012508</v>
+        <v>0.0005372</v>
       </c>
       <c r="D8" t="s">
         <v>3</v>
       </c>
       <c r="E8">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="F8">
-        <v>50.52691193458118</v>
+        <v>24.14213562373095</v>
       </c>
       <c r="G8">
-        <v>103</v>
+        <v>32</v>
       </c>
       <c r="H8">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="I8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J8">
-        <v>148</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B9">
         <v>32</v>
       </c>
       <c r="C9">
-        <v>0.0017691</v>
+        <v>0.0034743</v>
       </c>
       <c r="D9" t="s">
         <v>3</v>
@@ -707,228 +713,228 @@
         <v>49.698484809835</v>
       </c>
       <c r="G9">
-        <v>127</v>
+        <v>76</v>
       </c>
       <c r="H9">
-        <v>132</v>
+        <v>241</v>
       </c>
       <c r="I9">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J9">
-        <v>259</v>
+        <v>317</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B10">
         <v>32</v>
       </c>
       <c r="C10">
-        <v>0.0010452</v>
+        <v>0.0011258</v>
       </c>
       <c r="D10" t="s">
         <v>3</v>
       </c>
       <c r="E10">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="F10">
-        <v>49.69848480983499</v>
+        <v>49.698484809835</v>
       </c>
       <c r="G10">
-        <v>14</v>
+        <v>147</v>
       </c>
       <c r="H10">
-        <v>38</v>
+        <v>201</v>
       </c>
       <c r="I10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J10">
-        <v>52</v>
+        <v>348</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B11">
         <v>32</v>
       </c>
       <c r="C11">
-        <v>0.0034012</v>
+        <v>0.0013158</v>
       </c>
       <c r="D11" t="s">
         <v>3</v>
       </c>
       <c r="E11">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="F11">
-        <v>46.99910636312252</v>
+        <v>50.52691193458118</v>
       </c>
       <c r="G11">
-        <v>76</v>
+        <v>103</v>
       </c>
       <c r="H11">
-        <v>241</v>
+        <v>45</v>
       </c>
       <c r="I11">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J11">
-        <v>317</v>
+        <v>148</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B12">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="C12">
-        <v>0.0238787</v>
+        <v>0.0018366</v>
       </c>
       <c r="D12" t="s">
         <v>3</v>
       </c>
       <c r="E12">
-        <v>84</v>
+        <v>42</v>
       </c>
       <c r="F12">
-        <v>100.8111831820431</v>
+        <v>49.698484809835</v>
       </c>
       <c r="G12">
-        <v>166</v>
+        <v>127</v>
       </c>
       <c r="H12">
-        <v>983</v>
+        <v>132</v>
       </c>
       <c r="I12">
         <v>14</v>
       </c>
       <c r="J12">
-        <v>1149</v>
+        <v>259</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B13">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="C13">
-        <v>0.005478100000000001</v>
+        <v>0.0010794</v>
       </c>
       <c r="D13" t="s">
         <v>3</v>
       </c>
       <c r="E13">
-        <v>84</v>
+        <v>17</v>
       </c>
       <c r="F13">
-        <v>103.2964645562817</v>
+        <v>49.69848480983499</v>
       </c>
       <c r="G13">
-        <v>264</v>
+        <v>14</v>
       </c>
       <c r="H13">
-        <v>142</v>
+        <v>38</v>
       </c>
       <c r="I13">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="J13">
-        <v>406</v>
+        <v>52</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B14">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="C14">
-        <v>0.0118224</v>
+        <v>0.0035126</v>
       </c>
       <c r="D14" t="s">
         <v>3</v>
       </c>
       <c r="E14">
-        <v>84</v>
+        <v>6</v>
       </c>
       <c r="F14">
-        <v>100.8111831820431</v>
+        <v>46.86645192953345</v>
       </c>
       <c r="G14">
-        <v>326</v>
+        <v>76</v>
       </c>
       <c r="H14">
-        <v>515</v>
+        <v>241</v>
       </c>
       <c r="I14">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="J14">
-        <v>841</v>
+        <v>317</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B15">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="C15">
-        <v>0.0034616</v>
+        <v>0.003432800000000001</v>
       </c>
       <c r="D15" t="s">
         <v>3</v>
       </c>
       <c r="E15">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="F15">
-        <v>100.8111831820431</v>
+        <v>49.698484809835</v>
       </c>
       <c r="G15">
-        <v>15</v>
+        <v>66</v>
       </c>
       <c r="H15">
-        <v>39</v>
+        <v>250</v>
       </c>
       <c r="I15">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J15">
-        <v>54</v>
+        <v>316</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B16">
         <v>64</v>
       </c>
       <c r="C16">
-        <v>0.0230443</v>
+        <v>0.025808</v>
       </c>
       <c r="D16" t="s">
         <v>3</v>
       </c>
       <c r="E16">
-        <v>7</v>
+        <v>84</v>
       </c>
       <c r="F16">
-        <v>95.57049943528645</v>
+        <v>100.8111831820431</v>
       </c>
       <c r="G16">
         <v>166</v>
@@ -937,7 +943,7 @@
         <v>983</v>
       </c>
       <c r="I16">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J16">
         <v>1149</v>
@@ -945,109 +951,109 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B17">
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="C17">
-        <v>0.1490245</v>
+        <v>0.004922699999999999</v>
       </c>
       <c r="D17" t="s">
         <v>3</v>
       </c>
       <c r="E17">
-        <v>168</v>
+        <v>84</v>
       </c>
       <c r="F17">
-        <v>203.0365799264593</v>
+        <v>101.6396103067893</v>
       </c>
       <c r="G17">
-        <v>379</v>
+        <v>410</v>
       </c>
       <c r="H17">
-        <v>3979</v>
+        <v>814</v>
       </c>
       <c r="I17">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="J17">
-        <v>4358</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B18">
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="C18">
-        <v>0.0402807</v>
+        <v>0.005923699999999999</v>
       </c>
       <c r="D18" t="s">
         <v>3</v>
       </c>
       <c r="E18">
-        <v>168</v>
+        <v>84</v>
       </c>
       <c r="F18">
-        <v>208.0071426749365</v>
+        <v>103.2964645562817</v>
       </c>
       <c r="G18">
-        <v>643</v>
+        <v>264</v>
       </c>
       <c r="H18">
-        <v>587</v>
+        <v>142</v>
       </c>
       <c r="I18">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J18">
-        <v>1230</v>
+        <v>406</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B19">
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="C19">
-        <v>0.08020040000000001</v>
+        <v>0.0129962</v>
       </c>
       <c r="D19" t="s">
         <v>3</v>
       </c>
       <c r="E19">
-        <v>168</v>
+        <v>84</v>
       </c>
       <c r="F19">
-        <v>203.0365799264593</v>
+        <v>100.8111831820431</v>
       </c>
       <c r="G19">
-        <v>739</v>
+        <v>326</v>
       </c>
       <c r="H19">
-        <v>2026</v>
+        <v>515</v>
       </c>
       <c r="I19">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J19">
-        <v>2765</v>
+        <v>841</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B20">
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="C20">
-        <v>0.0140568</v>
+        <v>0.0036981</v>
       </c>
       <c r="D20" t="s">
         <v>3</v>
@@ -1056,30 +1062,30 @@
         <v>17</v>
       </c>
       <c r="F20">
-        <v>203.0365799264593</v>
+        <v>100.8111831820431</v>
       </c>
       <c r="G20">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H20">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I20">
         <v>7</v>
       </c>
       <c r="J20">
-        <v>59</v>
+        <v>54</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B21">
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="C21">
-        <v>0.1485451</v>
+        <v>0.0248513</v>
       </c>
       <c r="D21" t="s">
         <v>3</v>
@@ -1088,499 +1094,499 @@
         <v>7</v>
       </c>
       <c r="F21">
-        <v>191.4295326143042</v>
+        <v>95.40233038888984</v>
       </c>
       <c r="G21">
-        <v>379</v>
+        <v>166</v>
       </c>
       <c r="H21">
-        <v>3979</v>
+        <v>983</v>
       </c>
       <c r="I21">
         <v>5</v>
       </c>
       <c r="J21">
-        <v>4358</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B22">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="C22">
-        <v>0.0004585</v>
+        <v>0.0224448</v>
       </c>
       <c r="D22" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="E22">
-        <v>22</v>
+        <v>84</v>
       </c>
       <c r="F22">
-        <v>25.55634918610405</v>
+        <v>100.8111831820431</v>
       </c>
       <c r="G22">
-        <v>25</v>
+        <v>159</v>
       </c>
       <c r="H22">
-        <v>66</v>
+        <v>1005</v>
       </c>
       <c r="I22">
         <v>12</v>
       </c>
       <c r="J22">
-        <v>91</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B23">
-        <v>16</v>
+        <v>128</v>
       </c>
       <c r="C23">
-        <v>0.0005399</v>
+        <v>0.15967</v>
       </c>
       <c r="D23" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="E23">
-        <v>24</v>
+        <v>168</v>
       </c>
       <c r="F23">
-        <v>28.38477631085023</v>
+        <v>203.0365799264593</v>
       </c>
       <c r="G23">
-        <v>39</v>
+        <v>379</v>
       </c>
       <c r="H23">
-        <v>33</v>
+        <v>3979</v>
       </c>
       <c r="I23">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="J23">
-        <v>72</v>
+        <v>4358</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B24">
-        <v>16</v>
+        <v>128</v>
       </c>
       <c r="C24">
-        <v>0.0003932</v>
+        <v>0.0205536</v>
       </c>
       <c r="D24" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="E24">
-        <v>22</v>
+        <v>168</v>
       </c>
       <c r="F24">
-        <v>25.55634918610405</v>
+        <v>203.8650070512055</v>
       </c>
       <c r="G24">
-        <v>29</v>
+        <v>858</v>
       </c>
       <c r="H24">
-        <v>51</v>
+        <v>3328</v>
       </c>
       <c r="I24">
         <v>12</v>
       </c>
       <c r="J24">
-        <v>80</v>
+        <v>4186</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B25">
-        <v>16</v>
+        <v>128</v>
       </c>
       <c r="C25">
-        <v>0.0003333</v>
+        <v>0.0429991</v>
       </c>
       <c r="D25" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="E25">
-        <v>18</v>
+        <v>168</v>
       </c>
       <c r="F25">
-        <v>25.55634918610405</v>
+        <v>208.0071426749365</v>
       </c>
       <c r="G25">
-        <v>10</v>
+        <v>643</v>
       </c>
       <c r="H25">
-        <v>33</v>
+        <v>587</v>
       </c>
       <c r="I25">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="J25">
-        <v>43</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" t="s">
+        <v>13</v>
+      </c>
+      <c r="B26">
+        <v>128</v>
+      </c>
+      <c r="C26">
+        <v>0.08562030000000001</v>
+      </c>
+      <c r="D26" t="s">
+        <v>3</v>
+      </c>
+      <c r="E26">
+        <v>168</v>
+      </c>
+      <c r="F26">
+        <v>203.0365799264593</v>
+      </c>
+      <c r="G26">
+        <v>739</v>
+      </c>
+      <c r="H26">
+        <v>2026</v>
+      </c>
+      <c r="I26">
         <v>14</v>
       </c>
-      <c r="B26">
-        <v>16</v>
-      </c>
-      <c r="C26">
-        <v>0.000512</v>
-      </c>
-      <c r="D26" t="s">
-        <v>15</v>
-      </c>
-      <c r="E26">
-        <v>8</v>
-      </c>
-      <c r="F26">
-        <v>24.41488446708389</v>
-      </c>
-      <c r="G26">
-        <v>25</v>
-      </c>
-      <c r="H26">
-        <v>66</v>
-      </c>
-      <c r="I26">
-        <v>6</v>
-      </c>
       <c r="J26">
-        <v>91</v>
+        <v>2765</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B27">
-        <v>32</v>
+        <v>128</v>
       </c>
       <c r="C27">
-        <v>0.0028168</v>
+        <v>0.0150779</v>
       </c>
       <c r="D27" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="E27">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="F27">
-        <v>51.69848480983499</v>
+        <v>203.0365799264593</v>
       </c>
       <c r="G27">
-        <v>63</v>
+        <v>18</v>
       </c>
       <c r="H27">
-        <v>258</v>
+        <v>41</v>
       </c>
       <c r="I27">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="J27">
-        <v>321</v>
+        <v>59</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B28">
-        <v>32</v>
+        <v>128</v>
       </c>
       <c r="C28">
-        <v>0.0018485</v>
+        <v>0.1598635</v>
       </c>
       <c r="D28" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="E28">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="F28">
-        <v>52.52691193458119</v>
+        <v>191.4295326143042</v>
       </c>
       <c r="G28">
-        <v>105</v>
+        <v>379</v>
       </c>
       <c r="H28">
-        <v>77</v>
+        <v>3979</v>
       </c>
       <c r="I28">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="J28">
-        <v>182</v>
+        <v>4358</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B29">
-        <v>32</v>
+        <v>128</v>
       </c>
       <c r="C29">
-        <v>0.0023093</v>
+        <v>0.1517371</v>
       </c>
       <c r="D29" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="E29">
-        <v>44</v>
+        <v>168</v>
       </c>
       <c r="F29">
-        <v>51.69848480983499</v>
+        <v>203.0365799264593</v>
       </c>
       <c r="G29">
-        <v>107</v>
+        <v>373</v>
       </c>
       <c r="H29">
-        <v>200</v>
+        <v>4034</v>
       </c>
       <c r="I29">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J29">
-        <v>307</v>
+        <v>4407</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B30">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="C30">
-        <v>0.0009808</v>
+        <v>0.0005046</v>
       </c>
       <c r="D30" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E30">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F30">
-        <v>51.69848480983499</v>
+        <v>25.55634918610405</v>
       </c>
       <c r="G30">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="H30">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="I30">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J30">
-        <v>56</v>
+        <v>91</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B31">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="C31">
-        <v>0.0029314</v>
+        <v>0.0003077</v>
       </c>
       <c r="D31" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E31">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="F31">
-        <v>49.03946295574199</v>
+        <v>26.38477631085023</v>
       </c>
       <c r="G31">
-        <v>63</v>
+        <v>31</v>
       </c>
       <c r="H31">
-        <v>258</v>
+        <v>56</v>
       </c>
       <c r="I31">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J31">
-        <v>321</v>
+        <v>87</v>
       </c>
     </row>
     <row r="32" spans="1:10">
       <c r="A32" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B32">
-        <v>64</v>
+        <v>16</v>
       </c>
       <c r="C32">
-        <v>0.0190411</v>
+        <v>0.00055</v>
       </c>
       <c r="D32" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E32">
-        <v>88</v>
+        <v>24</v>
       </c>
       <c r="F32">
-        <v>103.9827560572969</v>
+        <v>28.38477631085023</v>
       </c>
       <c r="G32">
-        <v>160</v>
+        <v>39</v>
       </c>
       <c r="H32">
-        <v>1037</v>
+        <v>33</v>
       </c>
       <c r="I32">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="J32">
-        <v>1197</v>
+        <v>72</v>
       </c>
     </row>
     <row r="33" spans="1:10">
       <c r="A33" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B33">
-        <v>64</v>
+        <v>16</v>
       </c>
       <c r="C33">
-        <v>0.0163242</v>
+        <v>0.0004154</v>
       </c>
       <c r="D33" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E33">
-        <v>88</v>
+        <v>22</v>
       </c>
       <c r="F33">
-        <v>107.2964645562817</v>
+        <v>25.55634918610405</v>
       </c>
       <c r="G33">
-        <v>331</v>
+        <v>29</v>
       </c>
       <c r="H33">
-        <v>395</v>
+        <v>51</v>
       </c>
       <c r="I33">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="J33">
-        <v>726</v>
+        <v>80</v>
       </c>
     </row>
     <row r="34" spans="1:10">
       <c r="A34" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B34">
-        <v>64</v>
+        <v>16</v>
       </c>
       <c r="C34">
-        <v>0.0154216</v>
+        <v>0.0003521</v>
       </c>
       <c r="D34" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E34">
-        <v>88</v>
+        <v>18</v>
       </c>
       <c r="F34">
-        <v>103.9827560572969</v>
+        <v>25.55634918610405</v>
       </c>
       <c r="G34">
-        <v>260</v>
+        <v>10</v>
       </c>
       <c r="H34">
-        <v>758</v>
+        <v>33</v>
       </c>
       <c r="I34">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J34">
-        <v>1018</v>
+        <v>43</v>
       </c>
     </row>
     <row r="35" spans="1:10">
       <c r="A35" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B35">
-        <v>64</v>
+        <v>16</v>
       </c>
       <c r="C35">
-        <v>0.003392399999999999</v>
+        <v>0.0006652</v>
       </c>
       <c r="D35" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E35">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="F35">
-        <v>103.9827560572969</v>
+        <v>24.2748964148517</v>
       </c>
       <c r="G35">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="H35">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="I35">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="J35">
-        <v>57</v>
+        <v>91</v>
       </c>
     </row>
     <row r="36" spans="1:10">
       <c r="A36" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B36">
-        <v>64</v>
+        <v>16</v>
       </c>
       <c r="C36">
-        <v>0.0183713</v>
+        <v>0.0007118000000000001</v>
       </c>
       <c r="D36" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E36">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="F36">
-        <v>99.30085278599736</v>
+        <v>25.55634918610405</v>
       </c>
       <c r="G36">
-        <v>160</v>
+        <v>24</v>
       </c>
       <c r="H36">
-        <v>1037</v>
+        <v>69</v>
       </c>
       <c r="I36">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J36">
-        <v>1197</v>
+        <v>93</v>
       </c>
     </row>
     <row r="37" spans="1:10">
@@ -1588,31 +1594,31 @@
         <v>10</v>
       </c>
       <c r="B37">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="C37">
-        <v>0.121997</v>
+        <v>0.0029849</v>
       </c>
       <c r="D37" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E37">
-        <v>176</v>
+        <v>44</v>
       </c>
       <c r="F37">
-        <v>208.5512985522207</v>
+        <v>51.69848480983499</v>
       </c>
       <c r="G37">
-        <v>362</v>
+        <v>63</v>
       </c>
       <c r="H37">
-        <v>4153</v>
+        <v>258</v>
       </c>
       <c r="I37">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="J37">
-        <v>4515</v>
+        <v>321</v>
       </c>
     </row>
     <row r="38" spans="1:10">
@@ -1620,31 +1626,31 @@
         <v>11</v>
       </c>
       <c r="B38">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="C38">
-        <v>0.1526633</v>
+        <v>0.0012901</v>
       </c>
       <c r="D38" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E38">
-        <v>176</v>
+        <v>44</v>
       </c>
       <c r="F38">
-        <v>214.350288425444</v>
+        <v>52.52691193458119</v>
       </c>
       <c r="G38">
-        <v>836</v>
+        <v>106</v>
       </c>
       <c r="H38">
-        <v>1847</v>
+        <v>228</v>
       </c>
       <c r="I38">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="J38">
-        <v>2683</v>
+        <v>334</v>
       </c>
     </row>
     <row r="39" spans="1:10">
@@ -1652,31 +1658,31 @@
         <v>12</v>
       </c>
       <c r="B39">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="C39">
-        <v>0.1059115</v>
+        <v>0.0019769</v>
       </c>
       <c r="D39" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E39">
-        <v>176</v>
+        <v>44</v>
       </c>
       <c r="F39">
-        <v>208.5512985522207</v>
+        <v>52.52691193458119</v>
       </c>
       <c r="G39">
-        <v>554</v>
+        <v>105</v>
       </c>
       <c r="H39">
-        <v>2986</v>
+        <v>77</v>
       </c>
       <c r="I39">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J39">
-        <v>3540</v>
+        <v>182</v>
       </c>
     </row>
     <row r="40" spans="1:10">
@@ -1684,31 +1690,31 @@
         <v>13</v>
       </c>
       <c r="B40">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="C40">
-        <v>0.0122929</v>
+        <v>0.002414</v>
       </c>
       <c r="D40" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E40">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="F40">
-        <v>208.5512985522207</v>
+        <v>51.69848480983499</v>
       </c>
       <c r="G40">
-        <v>14</v>
+        <v>107</v>
       </c>
       <c r="H40">
-        <v>43</v>
+        <v>200</v>
       </c>
       <c r="I40">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J40">
-        <v>57</v>
+        <v>307</v>
       </c>
     </row>
     <row r="41" spans="1:10">
@@ -1716,991 +1722,991 @@
         <v>14</v>
       </c>
       <c r="B41">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="C41">
-        <v>0.1215531</v>
+        <v>0.0010381</v>
       </c>
       <c r="D41" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E41">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F41">
-        <v>198.924964802366</v>
+        <v>51.69848480983499</v>
       </c>
       <c r="G41">
-        <v>362</v>
+        <v>13</v>
       </c>
       <c r="H41">
-        <v>4153</v>
+        <v>43</v>
       </c>
       <c r="I41">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="J41">
-        <v>4515</v>
+        <v>56</v>
       </c>
     </row>
     <row r="42" spans="1:10">
       <c r="A42" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="B42">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="C42">
-        <v>0.0003786</v>
+        <v>0.0030295</v>
       </c>
       <c r="D42" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E42">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="F42">
-        <v>25.31370849898476</v>
+        <v>49.02879559762351</v>
       </c>
       <c r="G42">
-        <v>13</v>
+        <v>63</v>
       </c>
       <c r="H42">
-        <v>59</v>
+        <v>258</v>
       </c>
       <c r="I42">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="J42">
-        <v>72</v>
+        <v>321</v>
       </c>
     </row>
     <row r="43" spans="1:10">
       <c r="A43" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B43">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="C43">
-        <v>0.0002895</v>
+        <v>0.0029012</v>
       </c>
       <c r="D43" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E43">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="F43">
-        <v>26.72792206135786</v>
+        <v>51.69848480983499</v>
       </c>
       <c r="G43">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="H43">
-        <v>25</v>
+        <v>266</v>
       </c>
       <c r="I43">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J43">
-        <v>44</v>
+        <v>319</v>
       </c>
     </row>
     <row r="44" spans="1:10">
       <c r="A44" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B44">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="C44">
-        <v>0.0003137</v>
+        <v>0.0196066</v>
       </c>
       <c r="D44" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E44">
-        <v>23</v>
+        <v>88</v>
       </c>
       <c r="F44">
-        <v>25.31370849898476</v>
+        <v>103.9827560572969</v>
       </c>
       <c r="G44">
+        <v>160</v>
+      </c>
+      <c r="H44">
+        <v>1037</v>
+      </c>
+      <c r="I44">
         <v>18</v>
       </c>
-      <c r="H44">
-        <v>47</v>
-      </c>
-      <c r="I44">
-        <v>13</v>
-      </c>
       <c r="J44">
-        <v>65</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="45" spans="1:10">
       <c r="A45" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B45">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="C45">
-        <v>0.0003942</v>
+        <v>0.0051455</v>
       </c>
       <c r="D45" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E45">
-        <v>17</v>
+        <v>88</v>
       </c>
       <c r="F45">
-        <v>25.31370849898476</v>
+        <v>104.8111831820431</v>
       </c>
       <c r="G45">
-        <v>4</v>
+        <v>325</v>
       </c>
       <c r="H45">
-        <v>37</v>
+        <v>893</v>
       </c>
       <c r="I45">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J45">
-        <v>41</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="46" spans="1:10">
       <c r="A46" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B46">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="C46">
-        <v>0.0004014</v>
+        <v>0.0173749</v>
       </c>
       <c r="D46" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E46">
-        <v>11</v>
+        <v>88</v>
       </c>
       <c r="F46">
-        <v>24.55639589508264</v>
+        <v>107.2964645562817</v>
       </c>
       <c r="G46">
-        <v>13</v>
+        <v>331</v>
       </c>
       <c r="H46">
-        <v>59</v>
+        <v>395</v>
       </c>
       <c r="I46">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="J46">
-        <v>72</v>
+        <v>726</v>
       </c>
     </row>
     <row r="47" spans="1:10">
       <c r="A47" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B47">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="C47">
-        <v>0.002459499999999999</v>
+        <v>0.0163651</v>
       </c>
       <c r="D47" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E47">
-        <v>46</v>
+        <v>88</v>
       </c>
       <c r="F47">
-        <v>52.04163056034262</v>
+        <v>103.9827560572969</v>
       </c>
       <c r="G47">
-        <v>44</v>
+        <v>260</v>
       </c>
       <c r="H47">
-        <v>244</v>
+        <v>758</v>
       </c>
       <c r="I47">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J47">
-        <v>288</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="48" spans="1:10">
       <c r="A48" t="s">
+        <v>14</v>
+      </c>
+      <c r="B48">
+        <v>64</v>
+      </c>
+      <c r="C48">
+        <v>0.0034979</v>
+      </c>
+      <c r="D48" t="s">
+        <v>17</v>
+      </c>
+      <c r="E48">
+        <v>19</v>
+      </c>
+      <c r="F48">
+        <v>103.9827560572969</v>
+      </c>
+      <c r="G48">
+        <v>13</v>
+      </c>
+      <c r="H48">
+        <v>44</v>
+      </c>
+      <c r="I48">
         <v>11</v>
       </c>
-      <c r="B48">
-        <v>32</v>
-      </c>
-      <c r="C48">
-        <v>0.0013014</v>
-      </c>
-      <c r="D48" t="s">
-        <v>16</v>
-      </c>
-      <c r="E48">
-        <v>48</v>
-      </c>
-      <c r="F48">
-        <v>54.04163056034262</v>
-      </c>
-      <c r="G48">
-        <v>67</v>
-      </c>
-      <c r="H48">
-        <v>64</v>
-      </c>
-      <c r="I48">
-        <v>16</v>
-      </c>
       <c r="J48">
-        <v>131</v>
+        <v>57</v>
       </c>
     </row>
     <row r="49" spans="1:10">
       <c r="A49" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B49">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="C49">
-        <v>0.0018837</v>
+        <v>0.0197748</v>
       </c>
       <c r="D49" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E49">
-        <v>46</v>
+        <v>7</v>
       </c>
       <c r="F49">
-        <v>52.04163056034262</v>
+        <v>99.29815720118604</v>
       </c>
       <c r="G49">
-        <v>55</v>
+        <v>160</v>
       </c>
       <c r="H49">
-        <v>179</v>
+        <v>1037</v>
       </c>
       <c r="I49">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="J49">
-        <v>234</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="50" spans="1:10">
       <c r="A50" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B50">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="C50">
-        <v>0.0012408</v>
+        <v>0.0183939</v>
       </c>
       <c r="D50" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E50">
-        <v>24</v>
+        <v>88</v>
       </c>
       <c r="F50">
-        <v>52.04163056034262</v>
+        <v>103.9827560572969</v>
       </c>
       <c r="G50">
-        <v>5</v>
+        <v>138</v>
       </c>
       <c r="H50">
-        <v>59</v>
+        <v>1058</v>
       </c>
       <c r="I50">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J50">
-        <v>64</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="51" spans="1:10">
       <c r="A51" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B51">
+        <v>128</v>
+      </c>
+      <c r="C51">
+        <v>0.1302875</v>
+      </c>
+      <c r="D51" t="s">
+        <v>17</v>
+      </c>
+      <c r="E51">
+        <v>176</v>
+      </c>
+      <c r="F51">
+        <v>208.5512985522207</v>
+      </c>
+      <c r="G51">
+        <v>362</v>
+      </c>
+      <c r="H51">
+        <v>4153</v>
+      </c>
+      <c r="I51">
         <v>32</v>
       </c>
-      <c r="C51">
-        <v>0.0025718</v>
-      </c>
-      <c r="D51" t="s">
-        <v>16</v>
-      </c>
-      <c r="E51">
-        <v>11</v>
-      </c>
-      <c r="F51">
-        <v>49.99028453499244</v>
-      </c>
-      <c r="G51">
-        <v>44</v>
-      </c>
-      <c r="H51">
-        <v>244</v>
-      </c>
-      <c r="I51">
-        <v>9</v>
-      </c>
       <c r="J51">
-        <v>288</v>
+        <v>4515</v>
       </c>
     </row>
     <row r="52" spans="1:10">
       <c r="A52" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B52">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="C52">
-        <v>0.015765</v>
+        <v>0.0220098</v>
       </c>
       <c r="D52" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E52">
-        <v>92</v>
+        <v>176</v>
       </c>
       <c r="F52">
-        <v>105.4974746830583</v>
+        <v>209.3797256769669</v>
       </c>
       <c r="G52">
-        <v>124</v>
+        <v>892</v>
       </c>
       <c r="H52">
-        <v>980</v>
+        <v>3629</v>
       </c>
       <c r="I52">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J52">
-        <v>1104</v>
+        <v>4521</v>
       </c>
     </row>
     <row r="53" spans="1:10">
       <c r="A53" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B53">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="C53">
-        <v>0.008706700000000001</v>
+        <v>0.1626759</v>
       </c>
       <c r="D53" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E53">
-        <v>92</v>
+        <v>176</v>
       </c>
       <c r="F53">
-        <v>106.3259018078045</v>
+        <v>214.350288425444</v>
       </c>
       <c r="G53">
-        <v>229</v>
+        <v>836</v>
       </c>
       <c r="H53">
-        <v>267</v>
+        <v>1847</v>
       </c>
       <c r="I53">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J53">
-        <v>496</v>
+        <v>2683</v>
       </c>
     </row>
     <row r="54" spans="1:10">
       <c r="A54" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B54">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="C54">
-        <v>0.0125769</v>
+        <v>0.1147033</v>
       </c>
       <c r="D54" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E54">
-        <v>92</v>
+        <v>176</v>
       </c>
       <c r="F54">
-        <v>105.4974746830583</v>
+        <v>208.5512985522207</v>
       </c>
       <c r="G54">
-        <v>122</v>
+        <v>554</v>
       </c>
       <c r="H54">
-        <v>700</v>
+        <v>2986</v>
       </c>
       <c r="I54">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J54">
-        <v>822</v>
+        <v>3540</v>
       </c>
     </row>
     <row r="55" spans="1:10">
       <c r="A55" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B55">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="C55">
-        <v>0.0046645</v>
+        <v>0.0127862</v>
       </c>
       <c r="D55" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E55">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F55">
-        <v>105.4974746830583</v>
+        <v>208.5512985522207</v>
       </c>
       <c r="G55">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="H55">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="I55">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J55">
-        <v>67</v>
+        <v>57</v>
       </c>
     </row>
     <row r="56" spans="1:10">
       <c r="A56" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B56">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="C56">
-        <v>0.0172327</v>
+        <v>0.1311289</v>
       </c>
       <c r="D56" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E56">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F56">
-        <v>100.6498597519346</v>
+        <v>198.9242808865375</v>
       </c>
       <c r="G56">
-        <v>124</v>
+        <v>362</v>
       </c>
       <c r="H56">
-        <v>980</v>
+        <v>4153</v>
       </c>
       <c r="I56">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J56">
-        <v>1104</v>
+        <v>4515</v>
       </c>
     </row>
     <row r="57" spans="1:10">
       <c r="A57" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B57">
         <v>128</v>
       </c>
       <c r="C57">
-        <v>0.1020895</v>
+        <v>0.1253862</v>
       </c>
       <c r="D57" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E57">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="F57">
-        <v>212.4091629284898</v>
+        <v>208.5512985522207</v>
       </c>
       <c r="G57">
-        <v>266</v>
+        <v>322</v>
       </c>
       <c r="H57">
-        <v>3919</v>
+        <v>4201</v>
       </c>
       <c r="I57">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J57">
-        <v>4185</v>
+        <v>4523</v>
       </c>
     </row>
     <row r="58" spans="1:10">
       <c r="A58" t="s">
+        <v>10</v>
+      </c>
+      <c r="B58">
+        <v>16</v>
+      </c>
+      <c r="C58">
+        <v>0.000411</v>
+      </c>
+      <c r="D58" t="s">
+        <v>18</v>
+      </c>
+      <c r="E58">
+        <v>23</v>
+      </c>
+      <c r="F58">
+        <v>25.31370849898476</v>
+      </c>
+      <c r="G58">
+        <v>13</v>
+      </c>
+      <c r="H58">
+        <v>59</v>
+      </c>
+      <c r="I58">
         <v>11</v>
       </c>
-      <c r="B58">
-        <v>128</v>
-      </c>
-      <c r="C58">
-        <v>0.0652737</v>
-      </c>
-      <c r="D58" t="s">
-        <v>16</v>
-      </c>
-      <c r="E58">
-        <v>184</v>
-      </c>
-      <c r="F58">
-        <v>214.0660171779821</v>
-      </c>
-      <c r="G58">
-        <v>544</v>
-      </c>
-      <c r="H58">
-        <v>1070</v>
-      </c>
-      <c r="I58">
-        <v>30</v>
-      </c>
       <c r="J58">
-        <v>1614</v>
+        <v>72</v>
       </c>
     </row>
     <row r="59" spans="1:10">
       <c r="A59" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B59">
-        <v>128</v>
+        <v>16</v>
       </c>
       <c r="C59">
-        <v>0.08295180000000001</v>
+        <v>0.000229</v>
       </c>
       <c r="D59" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E59">
-        <v>184</v>
+        <v>23</v>
       </c>
       <c r="F59">
-        <v>212.4091629284898</v>
+        <v>25.31370849898476</v>
       </c>
       <c r="G59">
-        <v>270</v>
+        <v>21</v>
       </c>
       <c r="H59">
-        <v>2767</v>
+        <v>45</v>
       </c>
       <c r="I59">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J59">
-        <v>3037</v>
+        <v>66</v>
       </c>
     </row>
     <row r="60" spans="1:10">
       <c r="A60" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B60">
-        <v>128</v>
+        <v>16</v>
       </c>
       <c r="C60">
-        <v>0.0199562</v>
+        <v>0.0003135</v>
       </c>
       <c r="D60" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E60">
         <v>24</v>
       </c>
       <c r="F60">
-        <v>212.4091629284898</v>
+        <v>26.72792206135786</v>
       </c>
       <c r="G60">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="H60">
-        <v>61</v>
+        <v>25</v>
       </c>
       <c r="I60">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J60">
-        <v>71</v>
+        <v>44</v>
       </c>
     </row>
     <row r="61" spans="1:10">
       <c r="A61" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B61">
-        <v>128</v>
+        <v>16</v>
       </c>
       <c r="C61">
-        <v>0.102782</v>
+        <v>0.0003295</v>
       </c>
       <c r="D61" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E61">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F61">
-        <v>203.2060918012439</v>
+        <v>25.31370849898476</v>
       </c>
       <c r="G61">
-        <v>266</v>
+        <v>18</v>
       </c>
       <c r="H61">
-        <v>3919</v>
+        <v>47</v>
       </c>
       <c r="I61">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J61">
-        <v>4185</v>
+        <v>65</v>
       </c>
     </row>
     <row r="62" spans="1:10">
       <c r="A62" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B62">
         <v>16</v>
       </c>
       <c r="C62">
-        <v>0.0005406</v>
+        <v>0.0004089</v>
       </c>
       <c r="D62" t="s">
+        <v>18</v>
+      </c>
+      <c r="E62">
         <v>17</v>
       </c>
-      <c r="E62">
-        <v>20</v>
-      </c>
       <c r="F62">
-        <v>23.55634918610405</v>
+        <v>25.31370849898476</v>
       </c>
       <c r="G62">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="H62">
-        <v>70</v>
+        <v>37</v>
       </c>
       <c r="I62">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J62">
-        <v>104</v>
+        <v>41</v>
       </c>
     </row>
     <row r="63" spans="1:10">
       <c r="A63" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B63">
         <v>16</v>
       </c>
       <c r="C63">
-        <v>0.000384</v>
+        <v>0.0004338</v>
       </c>
       <c r="D63" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E63">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F63">
-        <v>24.38477631085024</v>
+        <v>24.32285268768197</v>
       </c>
       <c r="G63">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="H63">
-        <v>21</v>
+        <v>59</v>
       </c>
       <c r="I63">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J63">
-        <v>59</v>
+        <v>72</v>
       </c>
     </row>
     <row r="64" spans="1:10">
       <c r="A64" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B64">
         <v>16</v>
       </c>
       <c r="C64">
-        <v>0.0004287</v>
+        <v>0.0004282</v>
       </c>
       <c r="D64" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E64">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F64">
-        <v>23.55634918610405</v>
+        <v>25.31370849898476</v>
       </c>
       <c r="G64">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="H64">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="I64">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J64">
-        <v>87</v>
+        <v>76</v>
       </c>
     </row>
     <row r="65" spans="1:10">
       <c r="A65" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B65">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="C65">
-        <v>0.0004063000000000001</v>
+        <v>0.0025615</v>
       </c>
       <c r="D65" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E65">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="F65">
-        <v>23.55634918610405</v>
+        <v>52.04163056034262</v>
       </c>
       <c r="G65">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="H65">
-        <v>37</v>
+        <v>244</v>
       </c>
       <c r="I65">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="J65">
-        <v>52</v>
+        <v>288</v>
       </c>
     </row>
     <row r="66" spans="1:10">
       <c r="A66" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B66">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="C66">
-        <v>0.0005910999999999999</v>
+        <v>0.0010567</v>
       </c>
       <c r="D66" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E66">
-        <v>7</v>
+        <v>46</v>
       </c>
       <c r="F66">
-        <v>22.57616073291973</v>
+        <v>52.87005768508881</v>
       </c>
       <c r="G66">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="H66">
-        <v>70</v>
+        <v>175</v>
       </c>
       <c r="I66">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="J66">
-        <v>104</v>
+        <v>243</v>
       </c>
     </row>
     <row r="67" spans="1:10">
       <c r="A67" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B67">
         <v>32</v>
       </c>
       <c r="C67">
-        <v>0.0035912</v>
+        <v>0.0014422</v>
       </c>
       <c r="D67" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E67">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="F67">
-        <v>48.52691193458118</v>
+        <v>54.04163056034262</v>
       </c>
       <c r="G67">
-        <v>114</v>
+        <v>67</v>
       </c>
       <c r="H67">
-        <v>276</v>
+        <v>64</v>
       </c>
       <c r="I67">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J67">
-        <v>390</v>
+        <v>131</v>
       </c>
     </row>
     <row r="68" spans="1:10">
       <c r="A68" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B68">
         <v>32</v>
       </c>
       <c r="C68">
-        <v>0.0013739</v>
+        <v>0.0020269</v>
       </c>
       <c r="D68" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E68">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="F68">
-        <v>50.18376618407358</v>
+        <v>52.04163056034262</v>
       </c>
       <c r="G68">
-        <v>91</v>
+        <v>55</v>
       </c>
       <c r="H68">
-        <v>61</v>
+        <v>179</v>
       </c>
       <c r="I68">
         <v>16</v>
       </c>
       <c r="J68">
-        <v>152</v>
+        <v>234</v>
       </c>
     </row>
     <row r="69" spans="1:10">
       <c r="A69" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B69">
         <v>32</v>
       </c>
       <c r="C69">
-        <v>0.0025759</v>
+        <v>0.0013142</v>
       </c>
       <c r="D69" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E69">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="F69">
-        <v>48.52691193458118</v>
+        <v>52.04163056034262</v>
       </c>
       <c r="G69">
-        <v>102</v>
+        <v>5</v>
       </c>
       <c r="H69">
-        <v>185</v>
+        <v>59</v>
       </c>
       <c r="I69">
         <v>14</v>
       </c>
       <c r="J69">
-        <v>287</v>
+        <v>64</v>
       </c>
     </row>
     <row r="70" spans="1:10">
       <c r="A70" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B70">
         <v>32</v>
       </c>
       <c r="C70">
-        <v>0.0012948</v>
+        <v>0.002598899999999999</v>
       </c>
       <c r="D70" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E70">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="F70">
-        <v>48.52691193458118</v>
+        <v>49.89643329835992</v>
       </c>
       <c r="G70">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="H70">
-        <v>59</v>
+        <v>244</v>
       </c>
       <c r="I70">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J70">
-        <v>79</v>
+        <v>288</v>
       </c>
     </row>
     <row r="71" spans="1:10">
       <c r="A71" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B71">
         <v>32</v>
       </c>
       <c r="C71">
-        <v>0.0036794</v>
+        <v>0.0024118</v>
       </c>
       <c r="D71" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E71">
-        <v>8</v>
+        <v>46</v>
       </c>
       <c r="F71">
-        <v>46.54043818792906</v>
+        <v>52.04163056034262</v>
       </c>
       <c r="G71">
-        <v>114</v>
+        <v>36</v>
       </c>
       <c r="H71">
-        <v>276</v>
+        <v>248</v>
       </c>
       <c r="I71">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J71">
-        <v>390</v>
+        <v>284</v>
       </c>
     </row>
     <row r="72" spans="1:10">
@@ -2711,28 +2717,28 @@
         <v>64</v>
       </c>
       <c r="C72">
-        <v>0.0287193</v>
+        <v>0.0168613</v>
       </c>
       <c r="D72" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E72">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="F72">
-        <v>98.46803743153546</v>
+        <v>105.4974746830583</v>
       </c>
       <c r="G72">
-        <v>352</v>
+        <v>124</v>
       </c>
       <c r="H72">
-        <v>1159</v>
+        <v>980</v>
       </c>
       <c r="I72">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J72">
-        <v>1511</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="73" spans="1:10">
@@ -2743,28 +2749,28 @@
         <v>64</v>
       </c>
       <c r="C73">
-        <v>0.0054597</v>
+        <v>0.004311999999999999</v>
       </c>
       <c r="D73" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E73">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="F73">
-        <v>102.3675323681472</v>
+        <v>106.3259018078045</v>
       </c>
       <c r="G73">
-        <v>230</v>
+        <v>174</v>
       </c>
       <c r="H73">
-        <v>160</v>
+        <v>718</v>
       </c>
       <c r="I73">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J73">
-        <v>390</v>
+        <v>892</v>
       </c>
     </row>
     <row r="74" spans="1:10">
@@ -2775,28 +2781,28 @@
         <v>64</v>
       </c>
       <c r="C74">
-        <v>0.01683</v>
+        <v>0.0093718</v>
       </c>
       <c r="D74" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E74">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="F74">
-        <v>98.46803743153546</v>
+        <v>106.3259018078045</v>
       </c>
       <c r="G74">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="H74">
-        <v>717</v>
+        <v>267</v>
       </c>
       <c r="I74">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="J74">
-        <v>957</v>
+        <v>496</v>
       </c>
     </row>
     <row r="75" spans="1:10">
@@ -2807,28 +2813,28 @@
         <v>64</v>
       </c>
       <c r="C75">
-        <v>0.004711600000000001</v>
+        <v>0.0135943</v>
       </c>
       <c r="D75" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E75">
-        <v>24</v>
+        <v>92</v>
       </c>
       <c r="F75">
-        <v>98.46803743153546</v>
+        <v>105.4974746830583</v>
       </c>
       <c r="G75">
-        <v>25</v>
+        <v>122</v>
       </c>
       <c r="H75">
-        <v>63</v>
+        <v>700</v>
       </c>
       <c r="I75">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="J75">
-        <v>88</v>
+        <v>822</v>
       </c>
     </row>
     <row r="76" spans="1:10">
@@ -2839,828 +2845,2108 @@
         <v>64</v>
       </c>
       <c r="C76">
-        <v>0.027812</v>
+        <v>0.004973300000000001</v>
       </c>
       <c r="D76" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E76">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="F76">
-        <v>92.90052844970226</v>
+        <v>105.4974746830583</v>
       </c>
       <c r="G76">
-        <v>352</v>
+        <v>7</v>
       </c>
       <c r="H76">
-        <v>1159</v>
+        <v>60</v>
       </c>
       <c r="I76">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="J76">
-        <v>1511</v>
+        <v>67</v>
       </c>
     </row>
     <row r="77" spans="1:10">
       <c r="A77" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="B77">
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="C77">
-        <v>0.208237</v>
+        <v>0.0171851</v>
       </c>
       <c r="D77" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E77">
-        <v>160</v>
+        <v>11</v>
       </c>
       <c r="F77">
-        <v>198.350288425444</v>
+        <v>100.5452364519071</v>
       </c>
       <c r="G77">
-        <v>873</v>
+        <v>124</v>
       </c>
       <c r="H77">
-        <v>4844</v>
+        <v>980</v>
       </c>
       <c r="I77">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="J77">
-        <v>5717</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="78" spans="1:10">
       <c r="A78" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B78">
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="C78">
-        <v>0.0346657</v>
+        <v>0.0149212</v>
       </c>
       <c r="D78" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E78">
-        <v>161</v>
+        <v>92</v>
       </c>
       <c r="F78">
-        <v>204.7350647362943</v>
+        <v>105.4974746830583</v>
       </c>
       <c r="G78">
-        <v>625</v>
+        <v>104</v>
       </c>
       <c r="H78">
-        <v>581</v>
+        <v>995</v>
       </c>
       <c r="I78">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="J78">
-        <v>1206</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="79" spans="1:10">
       <c r="A79" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B79">
         <v>128</v>
       </c>
       <c r="C79">
-        <v>0.1163257</v>
+        <v>0.1104541</v>
       </c>
       <c r="D79" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E79">
-        <v>160</v>
+        <v>184</v>
       </c>
       <c r="F79">
-        <v>198.350288425444</v>
+        <v>212.4091629284898</v>
       </c>
       <c r="G79">
-        <v>540</v>
+        <v>266</v>
       </c>
       <c r="H79">
-        <v>2864</v>
+        <v>3919</v>
       </c>
       <c r="I79">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="J79">
-        <v>3404</v>
+        <v>4185</v>
       </c>
     </row>
     <row r="80" spans="1:10">
       <c r="A80" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B80">
         <v>128</v>
       </c>
       <c r="C80">
-        <v>0.01906</v>
+        <v>0.0179439</v>
       </c>
       <c r="D80" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E80">
-        <v>22</v>
+        <v>184</v>
       </c>
       <c r="F80">
-        <v>198.350288425444</v>
+        <v>213.2375900532359</v>
       </c>
       <c r="G80">
-        <v>22</v>
+        <v>388</v>
       </c>
       <c r="H80">
-        <v>67</v>
+        <v>2910</v>
       </c>
       <c r="I80">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="J80">
-        <v>89</v>
+        <v>3298</v>
       </c>
     </row>
     <row r="81" spans="1:10">
       <c r="A81" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B81">
         <v>128</v>
       </c>
       <c r="C81">
-        <v>0.2072281999999999</v>
+        <v>0.07056939999999999</v>
       </c>
       <c r="D81" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E81">
-        <v>8</v>
+        <v>184</v>
       </c>
       <c r="F81">
-        <v>190.4679384542775</v>
+        <v>214.0660171779821</v>
       </c>
       <c r="G81">
-        <v>873</v>
+        <v>544</v>
       </c>
       <c r="H81">
-        <v>4844</v>
+        <v>1070</v>
       </c>
       <c r="I81">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="J81">
-        <v>5717</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="82" spans="1:10">
       <c r="A82" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B82">
-        <v>16</v>
+        <v>128</v>
       </c>
       <c r="C82">
-        <v>0.000717</v>
+        <v>0.08971359999999999</v>
       </c>
       <c r="D82" t="s">
         <v>18</v>
       </c>
       <c r="E82">
-        <v>19</v>
+        <v>184</v>
       </c>
       <c r="F82">
-        <v>22.97056274847714</v>
+        <v>212.4091629284898</v>
       </c>
       <c r="G82">
-        <v>73</v>
+        <v>270</v>
       </c>
       <c r="H82">
-        <v>77</v>
+        <v>2767</v>
       </c>
       <c r="I82">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="J82">
-        <v>150</v>
+        <v>3037</v>
       </c>
     </row>
     <row r="83" spans="1:10">
       <c r="A83" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B83">
-        <v>16</v>
+        <v>128</v>
       </c>
       <c r="C83">
-        <v>0.0004643000000000001</v>
+        <v>0.0216076</v>
       </c>
       <c r="D83" t="s">
         <v>18</v>
       </c>
       <c r="E83">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F83">
-        <v>24.38477631085024</v>
+        <v>212.4091629284898</v>
       </c>
       <c r="G83">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="H83">
-        <v>21</v>
+        <v>61</v>
       </c>
       <c r="I83">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="J83">
-        <v>63</v>
+        <v>71</v>
       </c>
     </row>
     <row r="84" spans="1:10">
       <c r="A84" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B84">
-        <v>16</v>
+        <v>128</v>
       </c>
       <c r="C84">
-        <v>0.0006058</v>
+        <v>0.1110167</v>
       </c>
       <c r="D84" t="s">
         <v>18</v>
       </c>
       <c r="E84">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F84">
-        <v>22.97056274847714</v>
+        <v>203.098893996986</v>
       </c>
       <c r="G84">
-        <v>71</v>
+        <v>266</v>
       </c>
       <c r="H84">
-        <v>53</v>
+        <v>3919</v>
       </c>
       <c r="I84">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J84">
-        <v>124</v>
+        <v>4185</v>
       </c>
     </row>
     <row r="85" spans="1:10">
       <c r="A85" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B85">
-        <v>16</v>
+        <v>128</v>
       </c>
       <c r="C85">
-        <v>0.0005839</v>
+        <v>0.0993503</v>
       </c>
       <c r="D85" t="s">
         <v>18</v>
       </c>
       <c r="E85">
-        <v>10</v>
+        <v>184</v>
       </c>
       <c r="F85">
-        <v>22.97056274847714</v>
+        <v>212.4091629284898</v>
       </c>
       <c r="G85">
-        <v>11</v>
+        <v>247</v>
       </c>
       <c r="H85">
-        <v>25</v>
+        <v>3952</v>
       </c>
       <c r="I85">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="J85">
-        <v>36</v>
+        <v>4199</v>
       </c>
     </row>
     <row r="86" spans="1:10">
       <c r="A86" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B86">
         <v>16</v>
       </c>
       <c r="C86">
-        <v>0.0008386999999999998</v>
+        <v>0.0006736</v>
       </c>
       <c r="D86" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E86">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F86">
-        <v>22.52730043086546</v>
+        <v>23.55634918610405</v>
       </c>
       <c r="G86">
-        <v>73</v>
+        <v>34</v>
       </c>
       <c r="H86">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="I86">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J86">
-        <v>150</v>
+        <v>104</v>
       </c>
     </row>
     <row r="87" spans="1:10">
       <c r="A87" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B87">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="C87">
-        <v>0.0055118</v>
+        <v>0.00026</v>
       </c>
       <c r="D87" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E87">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F87">
-        <v>47.35533905932738</v>
+        <v>24.38477631085024</v>
       </c>
       <c r="G87">
-        <v>252</v>
+        <v>41</v>
       </c>
       <c r="H87">
-        <v>296</v>
+        <v>48</v>
       </c>
       <c r="I87">
         <v>12</v>
       </c>
       <c r="J87">
-        <v>548</v>
+        <v>89</v>
       </c>
     </row>
     <row r="88" spans="1:10">
       <c r="A88" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B88">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="C88">
-        <v>0.001511</v>
+        <v>0.0003932000000000001</v>
       </c>
       <c r="D88" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E88">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F88">
-        <v>49.35533905932738</v>
+        <v>24.38477631085024</v>
       </c>
       <c r="G88">
-        <v>104</v>
+        <v>38</v>
       </c>
       <c r="H88">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="I88">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J88">
-        <v>162</v>
+        <v>59</v>
       </c>
     </row>
     <row r="89" spans="1:10">
       <c r="A89" t="s">
+        <v>13</v>
+      </c>
+      <c r="B89">
+        <v>16</v>
+      </c>
+      <c r="C89">
+        <v>0.000454</v>
+      </c>
+      <c r="D89" t="s">
+        <v>19</v>
+      </c>
+      <c r="E89">
+        <v>20</v>
+      </c>
+      <c r="F89">
+        <v>23.55634918610405</v>
+      </c>
+      <c r="G89">
+        <v>39</v>
+      </c>
+      <c r="H89">
+        <v>48</v>
+      </c>
+      <c r="I89">
         <v>12</v>
       </c>
-      <c r="B89">
-        <v>32</v>
-      </c>
-      <c r="C89">
-        <v>0.0034278</v>
-      </c>
-      <c r="D89" t="s">
-        <v>18</v>
-      </c>
-      <c r="E89">
-        <v>38</v>
-      </c>
-      <c r="F89">
-        <v>47.35533905932738</v>
-      </c>
-      <c r="G89">
-        <v>197</v>
-      </c>
-      <c r="H89">
-        <v>191</v>
-      </c>
-      <c r="I89">
-        <v>4</v>
-      </c>
       <c r="J89">
-        <v>388</v>
+        <v>87</v>
       </c>
     </row>
     <row r="90" spans="1:10">
       <c r="A90" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B90">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="C90">
-        <v>0.0020146</v>
+        <v>0.0004305</v>
       </c>
       <c r="D90" t="s">
+        <v>19</v>
+      </c>
+      <c r="E90">
         <v>18</v>
       </c>
-      <c r="E90">
-        <v>12</v>
-      </c>
       <c r="F90">
-        <v>47.35533905932738</v>
+        <v>23.55634918610405</v>
       </c>
       <c r="G90">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H90">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="I90">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J90">
-        <v>39</v>
+        <v>52</v>
       </c>
     </row>
     <row r="91" spans="1:10">
       <c r="A91" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B91">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="C91">
-        <v>0.0055471</v>
+        <v>0.0007059999999999999</v>
       </c>
       <c r="D91" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E91">
+        <v>6</v>
+      </c>
+      <c r="F91">
+        <v>22.56073125075471</v>
+      </c>
+      <c r="G91">
+        <v>34</v>
+      </c>
+      <c r="H91">
+        <v>70</v>
+      </c>
+      <c r="I91">
         <v>4</v>
       </c>
-      <c r="F91">
-        <v>46.02417147054884</v>
-      </c>
-      <c r="G91">
-        <v>252</v>
-      </c>
-      <c r="H91">
-        <v>296</v>
-      </c>
-      <c r="I91">
-        <v>2</v>
-      </c>
       <c r="J91">
-        <v>548</v>
+        <v>104</v>
       </c>
     </row>
     <row r="92" spans="1:10">
       <c r="A92" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B92">
-        <v>64</v>
+        <v>16</v>
       </c>
       <c r="C92">
-        <v>0.0465013</v>
+        <v>0.0006441000000000001</v>
       </c>
       <c r="D92" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E92">
-        <v>76</v>
+        <v>20</v>
       </c>
       <c r="F92">
-        <v>96.12489168102785</v>
+        <v>23.55634918610405</v>
       </c>
       <c r="G92">
-        <v>578</v>
+        <v>35</v>
       </c>
       <c r="H92">
-        <v>1204</v>
+        <v>71</v>
       </c>
       <c r="I92">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="J92">
-        <v>1782</v>
+        <v>106</v>
       </c>
     </row>
     <row r="93" spans="1:10">
       <c r="A93" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B93">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="C93">
-        <v>0.0108756</v>
+        <v>0.003875100000000001</v>
       </c>
       <c r="D93" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E93">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="F93">
-        <v>100.1248916810278</v>
+        <v>48.52691193458118</v>
       </c>
       <c r="G93">
-        <v>292</v>
+        <v>114</v>
       </c>
       <c r="H93">
-        <v>263</v>
+        <v>276</v>
       </c>
       <c r="I93">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="J93">
-        <v>555</v>
+        <v>390</v>
       </c>
     </row>
     <row r="94" spans="1:10">
       <c r="A94" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B94">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="C94">
-        <v>0.0223417</v>
+        <v>0.0011789</v>
       </c>
       <c r="D94" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E94">
-        <v>76</v>
+        <v>40</v>
       </c>
       <c r="F94">
-        <v>96.12489168102785</v>
+        <v>49.35533905932738</v>
       </c>
       <c r="G94">
-        <v>419</v>
+        <v>141</v>
       </c>
       <c r="H94">
-        <v>710</v>
+        <v>202</v>
       </c>
       <c r="I94">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J94">
-        <v>1129</v>
+        <v>343</v>
       </c>
     </row>
     <row r="95" spans="1:10">
       <c r="A95" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B95">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="C95">
-        <v>0.007431200000000001</v>
+        <v>0.0014195</v>
       </c>
       <c r="D95" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E95">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="F95">
-        <v>96.12489168102785</v>
+        <v>50.18376618407358</v>
       </c>
       <c r="G95">
-        <v>12</v>
+        <v>91</v>
       </c>
       <c r="H95">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="I95">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="J95">
-        <v>40</v>
+        <v>152</v>
       </c>
     </row>
     <row r="96" spans="1:10">
       <c r="A96" t="s">
+        <v>13</v>
+      </c>
+      <c r="B96">
+        <v>32</v>
+      </c>
+      <c r="C96">
+        <v>0.002692</v>
+      </c>
+      <c r="D96" t="s">
+        <v>19</v>
+      </c>
+      <c r="E96">
+        <v>40</v>
+      </c>
+      <c r="F96">
+        <v>48.52691193458118</v>
+      </c>
+      <c r="G96">
+        <v>102</v>
+      </c>
+      <c r="H96">
+        <v>185</v>
+      </c>
+      <c r="I96">
         <v>14</v>
       </c>
-      <c r="B96">
-        <v>64</v>
-      </c>
-      <c r="C96">
-        <v>0.04703710000000001</v>
-      </c>
-      <c r="D96" t="s">
-        <v>18</v>
-      </c>
-      <c r="E96">
-        <v>4</v>
-      </c>
-      <c r="F96">
-        <v>93.2032658581451</v>
-      </c>
-      <c r="G96">
-        <v>578</v>
-      </c>
-      <c r="H96">
-        <v>1204</v>
-      </c>
-      <c r="I96">
-        <v>2</v>
-      </c>
       <c r="J96">
-        <v>1782</v>
+        <v>287</v>
       </c>
     </row>
     <row r="97" spans="1:10">
       <c r="A97" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B97">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="C97">
-        <v>0.3183174</v>
+        <v>0.0013392</v>
       </c>
       <c r="D97" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E97">
-        <v>152</v>
+        <v>24</v>
       </c>
       <c r="F97">
-        <v>193.6639969244288</v>
+        <v>48.52691193458118</v>
       </c>
       <c r="G97">
-        <v>1281</v>
+        <v>20</v>
       </c>
       <c r="H97">
-        <v>4902</v>
+        <v>59</v>
       </c>
       <c r="I97">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="J97">
-        <v>6183</v>
+        <v>79</v>
       </c>
     </row>
     <row r="98" spans="1:10">
       <c r="A98" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B98">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="C98">
-        <v>0.092317</v>
+        <v>0.0039451</v>
       </c>
       <c r="D98" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E98">
-        <v>161</v>
+        <v>7</v>
       </c>
       <c r="F98">
-        <v>202.2497833620557</v>
+        <v>46.64209787065961</v>
       </c>
       <c r="G98">
-        <v>614</v>
+        <v>114</v>
       </c>
       <c r="H98">
-        <v>1176</v>
+        <v>276</v>
       </c>
       <c r="I98">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J98">
-        <v>1790</v>
+        <v>390</v>
       </c>
     </row>
     <row r="99" spans="1:10">
       <c r="A99" t="s">
+        <v>16</v>
+      </c>
+      <c r="B99">
+        <v>32</v>
+      </c>
+      <c r="C99">
+        <v>0.0044204</v>
+      </c>
+      <c r="D99" t="s">
+        <v>19</v>
+      </c>
+      <c r="E99">
+        <v>40</v>
+      </c>
+      <c r="F99">
+        <v>48.52691193458118</v>
+      </c>
+      <c r="G99">
+        <v>88</v>
+      </c>
+      <c r="H99">
+        <v>289</v>
+      </c>
+      <c r="I99">
         <v>12</v>
       </c>
-      <c r="B99">
-        <v>128</v>
-      </c>
-      <c r="C99">
-        <v>0.1514367</v>
-      </c>
-      <c r="D99" t="s">
-        <v>18</v>
-      </c>
-      <c r="E99">
-        <v>152</v>
-      </c>
-      <c r="F99">
-        <v>193.6639969244288</v>
-      </c>
-      <c r="G99">
-        <v>790</v>
-      </c>
-      <c r="H99">
-        <v>2816</v>
-      </c>
-      <c r="I99">
-        <v>4</v>
-      </c>
       <c r="J99">
-        <v>3606</v>
+        <v>377</v>
       </c>
     </row>
     <row r="100" spans="1:10">
       <c r="A100" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B100">
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="C100">
-        <v>0.030449</v>
+        <v>0.0296328</v>
       </c>
       <c r="D100" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E100">
-        <v>12</v>
+        <v>80</v>
       </c>
       <c r="F100">
-        <v>193.6639969244288</v>
+        <v>98.46803743153546</v>
       </c>
       <c r="G100">
-        <v>12</v>
+        <v>352</v>
       </c>
       <c r="H100">
-        <v>29</v>
+        <v>1159</v>
       </c>
       <c r="I100">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="J100">
-        <v>41</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="101" spans="1:10">
       <c r="A101" t="s">
+        <v>11</v>
+      </c>
+      <c r="B101">
+        <v>64</v>
+      </c>
+      <c r="C101">
+        <v>0.0051299</v>
+      </c>
+      <c r="D101" t="s">
+        <v>19</v>
+      </c>
+      <c r="E101">
+        <v>80</v>
+      </c>
+      <c r="F101">
+        <v>99.29646455628166</v>
+      </c>
+      <c r="G101">
+        <v>345</v>
+      </c>
+      <c r="H101">
+        <v>867</v>
+      </c>
+      <c r="I101">
         <v>14</v>
       </c>
-      <c r="B101">
+      <c r="J101">
+        <v>1212</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10">
+      <c r="A102" t="s">
+        <v>12</v>
+      </c>
+      <c r="B102">
+        <v>64</v>
+      </c>
+      <c r="C102">
+        <v>0.0058033</v>
+      </c>
+      <c r="D102" t="s">
+        <v>19</v>
+      </c>
+      <c r="E102">
+        <v>81</v>
+      </c>
+      <c r="F102">
+        <v>102.3675323681472</v>
+      </c>
+      <c r="G102">
+        <v>230</v>
+      </c>
+      <c r="H102">
+        <v>160</v>
+      </c>
+      <c r="I102">
+        <v>21</v>
+      </c>
+      <c r="J102">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10">
+      <c r="A103" t="s">
+        <v>13</v>
+      </c>
+      <c r="B103">
+        <v>64</v>
+      </c>
+      <c r="C103">
+        <v>0.0183267</v>
+      </c>
+      <c r="D103" t="s">
+        <v>19</v>
+      </c>
+      <c r="E103">
+        <v>80</v>
+      </c>
+      <c r="F103">
+        <v>98.46803743153546</v>
+      </c>
+      <c r="G103">
+        <v>240</v>
+      </c>
+      <c r="H103">
+        <v>717</v>
+      </c>
+      <c r="I103">
+        <v>14</v>
+      </c>
+      <c r="J103">
+        <v>957</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10">
+      <c r="A104" t="s">
+        <v>14</v>
+      </c>
+      <c r="B104">
+        <v>64</v>
+      </c>
+      <c r="C104">
+        <v>0.0050223</v>
+      </c>
+      <c r="D104" t="s">
+        <v>19</v>
+      </c>
+      <c r="E104">
+        <v>24</v>
+      </c>
+      <c r="F104">
+        <v>98.46803743153546</v>
+      </c>
+      <c r="G104">
+        <v>25</v>
+      </c>
+      <c r="H104">
+        <v>63</v>
+      </c>
+      <c r="I104">
+        <v>13</v>
+      </c>
+      <c r="J104">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10">
+      <c r="A105" t="s">
+        <v>15</v>
+      </c>
+      <c r="B105">
+        <v>64</v>
+      </c>
+      <c r="C105">
+        <v>0.029346</v>
+      </c>
+      <c r="D105" t="s">
+        <v>19</v>
+      </c>
+      <c r="E105">
+        <v>9</v>
+      </c>
+      <c r="F105">
+        <v>92.69991043961832</v>
+      </c>
+      <c r="G105">
+        <v>352</v>
+      </c>
+      <c r="H105">
+        <v>1159</v>
+      </c>
+      <c r="I105">
+        <v>7</v>
+      </c>
+      <c r="J105">
+        <v>1511</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10">
+      <c r="A106" t="s">
+        <v>16</v>
+      </c>
+      <c r="B106">
+        <v>64</v>
+      </c>
+      <c r="C106">
+        <v>0.0279673</v>
+      </c>
+      <c r="D106" t="s">
+        <v>19</v>
+      </c>
+      <c r="E106">
+        <v>80</v>
+      </c>
+      <c r="F106">
+        <v>98.46803743153546</v>
+      </c>
+      <c r="G106">
+        <v>286</v>
+      </c>
+      <c r="H106">
+        <v>1212</v>
+      </c>
+      <c r="I106">
+        <v>12</v>
+      </c>
+      <c r="J106">
+        <v>1498</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10">
+      <c r="A107" t="s">
+        <v>10</v>
+      </c>
+      <c r="B107">
         <v>128</v>
       </c>
-      <c r="C101">
-        <v>0.3183032</v>
-      </c>
-      <c r="D101" t="s">
+      <c r="C107">
+        <v>0.2242598</v>
+      </c>
+      <c r="D107" t="s">
+        <v>19</v>
+      </c>
+      <c r="E107">
+        <v>160</v>
+      </c>
+      <c r="F107">
+        <v>198.350288425444</v>
+      </c>
+      <c r="G107">
+        <v>873</v>
+      </c>
+      <c r="H107">
+        <v>4844</v>
+      </c>
+      <c r="I107">
+        <v>28</v>
+      </c>
+      <c r="J107">
+        <v>5717</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10">
+      <c r="A108" t="s">
+        <v>11</v>
+      </c>
+      <c r="B108">
+        <v>128</v>
+      </c>
+      <c r="C108">
+        <v>0.022055</v>
+      </c>
+      <c r="D108" t="s">
+        <v>19</v>
+      </c>
+      <c r="E108">
+        <v>160</v>
+      </c>
+      <c r="F108">
+        <v>199.1787155501902</v>
+      </c>
+      <c r="G108">
+        <v>899</v>
+      </c>
+      <c r="H108">
+        <v>3630</v>
+      </c>
+      <c r="I108">
+        <v>15</v>
+      </c>
+      <c r="J108">
+        <v>4529</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10">
+      <c r="A109" t="s">
+        <v>12</v>
+      </c>
+      <c r="B109">
+        <v>128</v>
+      </c>
+      <c r="C109">
+        <v>0.0368362</v>
+      </c>
+      <c r="D109" t="s">
+        <v>19</v>
+      </c>
+      <c r="E109">
+        <v>161</v>
+      </c>
+      <c r="F109">
+        <v>204.7350647362943</v>
+      </c>
+      <c r="G109">
+        <v>625</v>
+      </c>
+      <c r="H109">
+        <v>581</v>
+      </c>
+      <c r="I109">
+        <v>29</v>
+      </c>
+      <c r="J109">
+        <v>1206</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10">
+      <c r="A110" t="s">
+        <v>13</v>
+      </c>
+      <c r="B110">
+        <v>128</v>
+      </c>
+      <c r="C110">
+        <v>0.1254835</v>
+      </c>
+      <c r="D110" t="s">
+        <v>19</v>
+      </c>
+      <c r="E110">
+        <v>160</v>
+      </c>
+      <c r="F110">
+        <v>198.350288425444</v>
+      </c>
+      <c r="G110">
+        <v>540</v>
+      </c>
+      <c r="H110">
+        <v>2864</v>
+      </c>
+      <c r="I110">
+        <v>12</v>
+      </c>
+      <c r="J110">
+        <v>3404</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10">
+      <c r="A111" t="s">
+        <v>14</v>
+      </c>
+      <c r="B111">
+        <v>128</v>
+      </c>
+      <c r="C111">
+        <v>0.0206832</v>
+      </c>
+      <c r="D111" t="s">
+        <v>19</v>
+      </c>
+      <c r="E111">
+        <v>22</v>
+      </c>
+      <c r="F111">
+        <v>198.350288425444</v>
+      </c>
+      <c r="G111">
+        <v>22</v>
+      </c>
+      <c r="H111">
+        <v>67</v>
+      </c>
+      <c r="I111">
+        <v>9</v>
+      </c>
+      <c r="J111">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10">
+      <c r="A112" t="s">
+        <v>15</v>
+      </c>
+      <c r="B112">
+        <v>128</v>
+      </c>
+      <c r="C112">
+        <v>0.2232106</v>
+      </c>
+      <c r="D112" t="s">
+        <v>19</v>
+      </c>
+      <c r="E112">
+        <v>7</v>
+      </c>
+      <c r="F112">
+        <v>190.5463808779157</v>
+      </c>
+      <c r="G112">
+        <v>873</v>
+      </c>
+      <c r="H112">
+        <v>4844</v>
+      </c>
+      <c r="I112">
+        <v>5</v>
+      </c>
+      <c r="J112">
+        <v>5717</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10">
+      <c r="A113" t="s">
+        <v>16</v>
+      </c>
+      <c r="B113">
+        <v>128</v>
+      </c>
+      <c r="C113">
+        <v>0.2098544</v>
+      </c>
+      <c r="D113" t="s">
+        <v>19</v>
+      </c>
+      <c r="E113">
+        <v>160</v>
+      </c>
+      <c r="F113">
+        <v>198.350288425444</v>
+      </c>
+      <c r="G113">
+        <v>706</v>
+      </c>
+      <c r="H113">
+        <v>4951</v>
+      </c>
+      <c r="I113">
         <v>18</v>
       </c>
-      <c r="E101">
+      <c r="J113">
+        <v>5657</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10">
+      <c r="A114" t="s">
+        <v>10</v>
+      </c>
+      <c r="B114">
+        <v>16</v>
+      </c>
+      <c r="C114">
+        <v>0.0007793</v>
+      </c>
+      <c r="D114" t="s">
+        <v>20</v>
+      </c>
+      <c r="E114">
+        <v>19</v>
+      </c>
+      <c r="F114">
+        <v>22.97056274847714</v>
+      </c>
+      <c r="G114">
+        <v>73</v>
+      </c>
+      <c r="H114">
+        <v>77</v>
+      </c>
+      <c r="I114">
+        <v>5</v>
+      </c>
+      <c r="J114">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10">
+      <c r="A115" t="s">
+        <v>11</v>
+      </c>
+      <c r="B115">
+        <v>16</v>
+      </c>
+      <c r="C115">
+        <v>0.00029</v>
+      </c>
+      <c r="D115" t="s">
+        <v>20</v>
+      </c>
+      <c r="E115">
+        <v>19</v>
+      </c>
+      <c r="F115">
+        <v>22.97056274847714</v>
+      </c>
+      <c r="G115">
+        <v>67</v>
+      </c>
+      <c r="H115">
+        <v>45</v>
+      </c>
+      <c r="I115">
+        <v>5</v>
+      </c>
+      <c r="J115">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10">
+      <c r="A116" t="s">
+        <v>12</v>
+      </c>
+      <c r="B116">
+        <v>16</v>
+      </c>
+      <c r="C116">
+        <v>0.0004352</v>
+      </c>
+      <c r="D116" t="s">
+        <v>20</v>
+      </c>
+      <c r="E116">
+        <v>20</v>
+      </c>
+      <c r="F116">
+        <v>24.38477631085024</v>
+      </c>
+      <c r="G116">
+        <v>42</v>
+      </c>
+      <c r="H116">
+        <v>21</v>
+      </c>
+      <c r="I116">
+        <v>7</v>
+      </c>
+      <c r="J116">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10">
+      <c r="A117" t="s">
+        <v>13</v>
+      </c>
+      <c r="B117">
+        <v>16</v>
+      </c>
+      <c r="C117">
+        <v>0.0006098</v>
+      </c>
+      <c r="D117" t="s">
+        <v>20</v>
+      </c>
+      <c r="E117">
+        <v>19</v>
+      </c>
+      <c r="F117">
+        <v>22.97056274847714</v>
+      </c>
+      <c r="G117">
+        <v>71</v>
+      </c>
+      <c r="H117">
+        <v>53</v>
+      </c>
+      <c r="I117">
+        <v>3</v>
+      </c>
+      <c r="J117">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10">
+      <c r="A118" t="s">
+        <v>14</v>
+      </c>
+      <c r="B118">
+        <v>16</v>
+      </c>
+      <c r="C118">
+        <v>0.0006093</v>
+      </c>
+      <c r="D118" t="s">
+        <v>20</v>
+      </c>
+      <c r="E118">
+        <v>10</v>
+      </c>
+      <c r="F118">
+        <v>22.97056274847714</v>
+      </c>
+      <c r="G118">
+        <v>11</v>
+      </c>
+      <c r="H118">
+        <v>25</v>
+      </c>
+      <c r="I118">
+        <v>2</v>
+      </c>
+      <c r="J118">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10">
+      <c r="A119" t="s">
+        <v>15</v>
+      </c>
+      <c r="B119">
+        <v>16</v>
+      </c>
+      <c r="C119">
+        <v>0.0008636999999999999</v>
+      </c>
+      <c r="D119" t="s">
+        <v>20</v>
+      </c>
+      <c r="E119">
         <v>4</v>
       </c>
-      <c r="F101">
+      <c r="F119">
+        <v>22.52730043086546</v>
+      </c>
+      <c r="G119">
+        <v>73</v>
+      </c>
+      <c r="H119">
+        <v>77</v>
+      </c>
+      <c r="I119">
+        <v>2</v>
+      </c>
+      <c r="J119">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10">
+      <c r="A120" t="s">
+        <v>16</v>
+      </c>
+      <c r="B120">
+        <v>16</v>
+      </c>
+      <c r="C120">
+        <v>0.0009927</v>
+      </c>
+      <c r="D120" t="s">
+        <v>20</v>
+      </c>
+      <c r="E120">
+        <v>19</v>
+      </c>
+      <c r="F120">
+        <v>22.97056274847714</v>
+      </c>
+      <c r="G120">
+        <v>69</v>
+      </c>
+      <c r="H120">
+        <v>89</v>
+      </c>
+      <c r="I120">
+        <v>4</v>
+      </c>
+      <c r="J120">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10">
+      <c r="A121" t="s">
+        <v>10</v>
+      </c>
+      <c r="B121">
+        <v>32</v>
+      </c>
+      <c r="C121">
+        <v>0.0057743</v>
+      </c>
+      <c r="D121" t="s">
+        <v>20</v>
+      </c>
+      <c r="E121">
+        <v>38</v>
+      </c>
+      <c r="F121">
+        <v>47.35533905932738</v>
+      </c>
+      <c r="G121">
+        <v>252</v>
+      </c>
+      <c r="H121">
+        <v>296</v>
+      </c>
+      <c r="I121">
+        <v>12</v>
+      </c>
+      <c r="J121">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10">
+      <c r="A122" t="s">
+        <v>11</v>
+      </c>
+      <c r="B122">
+        <v>32</v>
+      </c>
+      <c r="C122">
+        <v>0.0009507</v>
+      </c>
+      <c r="D122" t="s">
+        <v>20</v>
+      </c>
+      <c r="E122">
+        <v>38</v>
+      </c>
+      <c r="F122">
+        <v>47.35533905932738</v>
+      </c>
+      <c r="G122">
+        <v>178</v>
+      </c>
+      <c r="H122">
+        <v>163</v>
+      </c>
+      <c r="I122">
+        <v>4</v>
+      </c>
+      <c r="J122">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10">
+      <c r="A123" t="s">
+        <v>12</v>
+      </c>
+      <c r="B123">
+        <v>32</v>
+      </c>
+      <c r="C123">
+        <v>0.0015813</v>
+      </c>
+      <c r="D123" t="s">
+        <v>20</v>
+      </c>
+      <c r="E123">
+        <v>40</v>
+      </c>
+      <c r="F123">
+        <v>49.35533905932738</v>
+      </c>
+      <c r="G123">
+        <v>104</v>
+      </c>
+      <c r="H123">
+        <v>58</v>
+      </c>
+      <c r="I123">
+        <v>8</v>
+      </c>
+      <c r="J123">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10">
+      <c r="A124" t="s">
+        <v>13</v>
+      </c>
+      <c r="B124">
+        <v>32</v>
+      </c>
+      <c r="C124">
+        <v>0.0035952</v>
+      </c>
+      <c r="D124" t="s">
+        <v>20</v>
+      </c>
+      <c r="E124">
+        <v>38</v>
+      </c>
+      <c r="F124">
+        <v>47.35533905932738</v>
+      </c>
+      <c r="G124">
+        <v>197</v>
+      </c>
+      <c r="H124">
+        <v>191</v>
+      </c>
+      <c r="I124">
+        <v>4</v>
+      </c>
+      <c r="J124">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10">
+      <c r="A125" t="s">
+        <v>14</v>
+      </c>
+      <c r="B125">
+        <v>32</v>
+      </c>
+      <c r="C125">
+        <v>0.0021138</v>
+      </c>
+      <c r="D125" t="s">
+        <v>20</v>
+      </c>
+      <c r="E125">
+        <v>12</v>
+      </c>
+      <c r="F125">
+        <v>47.35533905932738</v>
+      </c>
+      <c r="G125">
+        <v>10</v>
+      </c>
+      <c r="H125">
+        <v>29</v>
+      </c>
+      <c r="I125">
+        <v>3</v>
+      </c>
+      <c r="J125">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10">
+      <c r="A126" t="s">
+        <v>15</v>
+      </c>
+      <c r="B126">
+        <v>32</v>
+      </c>
+      <c r="C126">
+        <v>0.0058417</v>
+      </c>
+      <c r="D126" t="s">
+        <v>20</v>
+      </c>
+      <c r="E126">
+        <v>4</v>
+      </c>
+      <c r="F126">
+        <v>46.02417147054884</v>
+      </c>
+      <c r="G126">
+        <v>252</v>
+      </c>
+      <c r="H126">
+        <v>296</v>
+      </c>
+      <c r="I126">
+        <v>2</v>
+      </c>
+      <c r="J126">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10">
+      <c r="A127" t="s">
+        <v>16</v>
+      </c>
+      <c r="B127">
+        <v>32</v>
+      </c>
+      <c r="C127">
+        <v>0.007036299999999998</v>
+      </c>
+      <c r="D127" t="s">
+        <v>20</v>
+      </c>
+      <c r="E127">
+        <v>38</v>
+      </c>
+      <c r="F127">
+        <v>47.35533905932738</v>
+      </c>
+      <c r="G127">
+        <v>214</v>
+      </c>
+      <c r="H127">
+        <v>337</v>
+      </c>
+      <c r="I127">
+        <v>8</v>
+      </c>
+      <c r="J127">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10">
+      <c r="A128" t="s">
+        <v>10</v>
+      </c>
+      <c r="B128">
+        <v>64</v>
+      </c>
+      <c r="C128">
+        <v>0.0501117</v>
+      </c>
+      <c r="D128" t="s">
+        <v>20</v>
+      </c>
+      <c r="E128">
+        <v>76</v>
+      </c>
+      <c r="F128">
+        <v>96.12489168102785</v>
+      </c>
+      <c r="G128">
+        <v>578</v>
+      </c>
+      <c r="H128">
+        <v>1204</v>
+      </c>
+      <c r="I128">
+        <v>24</v>
+      </c>
+      <c r="J128">
+        <v>1782</v>
+      </c>
+    </row>
+    <row r="129" spans="1:10">
+      <c r="A129" t="s">
+        <v>11</v>
+      </c>
+      <c r="B129">
+        <v>64</v>
+      </c>
+      <c r="C129">
+        <v>0.0037831</v>
+      </c>
+      <c r="D129" t="s">
+        <v>20</v>
+      </c>
+      <c r="E129">
+        <v>76</v>
+      </c>
+      <c r="F129">
+        <v>96.12489168102785</v>
+      </c>
+      <c r="G129">
+        <v>402</v>
+      </c>
+      <c r="H129">
+        <v>629</v>
+      </c>
+      <c r="I129">
+        <v>6</v>
+      </c>
+      <c r="J129">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="130" spans="1:10">
+      <c r="A130" t="s">
+        <v>12</v>
+      </c>
+      <c r="B130">
+        <v>64</v>
+      </c>
+      <c r="C130">
+        <v>0.0118541</v>
+      </c>
+      <c r="D130" t="s">
+        <v>20</v>
+      </c>
+      <c r="E130">
+        <v>80</v>
+      </c>
+      <c r="F130">
+        <v>100.1248916810278</v>
+      </c>
+      <c r="G130">
+        <v>292</v>
+      </c>
+      <c r="H130">
+        <v>263</v>
+      </c>
+      <c r="I130">
+        <v>8</v>
+      </c>
+      <c r="J130">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="131" spans="1:10">
+      <c r="A131" t="s">
+        <v>13</v>
+      </c>
+      <c r="B131">
+        <v>64</v>
+      </c>
+      <c r="C131">
+        <v>0.023993</v>
+      </c>
+      <c r="D131" t="s">
+        <v>20</v>
+      </c>
+      <c r="E131">
+        <v>76</v>
+      </c>
+      <c r="F131">
+        <v>96.12489168102785</v>
+      </c>
+      <c r="G131">
+        <v>419</v>
+      </c>
+      <c r="H131">
+        <v>710</v>
+      </c>
+      <c r="I131">
+        <v>6</v>
+      </c>
+      <c r="J131">
+        <v>1129</v>
+      </c>
+    </row>
+    <row r="132" spans="1:10">
+      <c r="A132" t="s">
+        <v>14</v>
+      </c>
+      <c r="B132">
+        <v>64</v>
+      </c>
+      <c r="C132">
+        <v>0.0080479</v>
+      </c>
+      <c r="D132" t="s">
+        <v>20</v>
+      </c>
+      <c r="E132">
+        <v>12</v>
+      </c>
+      <c r="F132">
+        <v>96.12489168102785</v>
+      </c>
+      <c r="G132">
+        <v>12</v>
+      </c>
+      <c r="H132">
+        <v>28</v>
+      </c>
+      <c r="I132">
+        <v>3</v>
+      </c>
+      <c r="J132">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="133" spans="1:10">
+      <c r="A133" t="s">
+        <v>15</v>
+      </c>
+      <c r="B133">
+        <v>64</v>
+      </c>
+      <c r="C133">
+        <v>0.0502154</v>
+      </c>
+      <c r="D133" t="s">
+        <v>20</v>
+      </c>
+      <c r="E133">
+        <v>4</v>
+      </c>
+      <c r="F133">
+        <v>93.2032658581451</v>
+      </c>
+      <c r="G133">
+        <v>578</v>
+      </c>
+      <c r="H133">
+        <v>1204</v>
+      </c>
+      <c r="I133">
+        <v>2</v>
+      </c>
+      <c r="J133">
+        <v>1782</v>
+      </c>
+    </row>
+    <row r="134" spans="1:10">
+      <c r="A134" t="s">
+        <v>16</v>
+      </c>
+      <c r="B134">
+        <v>64</v>
+      </c>
+      <c r="C134">
+        <v>0.0504695</v>
+      </c>
+      <c r="D134" t="s">
+        <v>20</v>
+      </c>
+      <c r="E134">
+        <v>76</v>
+      </c>
+      <c r="F134">
+        <v>96.12489168102785</v>
+      </c>
+      <c r="G134">
+        <v>503</v>
+      </c>
+      <c r="H134">
+        <v>1301</v>
+      </c>
+      <c r="I134">
+        <v>14</v>
+      </c>
+      <c r="J134">
+        <v>1804</v>
+      </c>
+    </row>
+    <row r="135" spans="1:10">
+      <c r="A135" t="s">
+        <v>10</v>
+      </c>
+      <c r="B135">
+        <v>128</v>
+      </c>
+      <c r="C135">
+        <v>0.340181</v>
+      </c>
+      <c r="D135" t="s">
+        <v>20</v>
+      </c>
+      <c r="E135">
+        <v>152</v>
+      </c>
+      <c r="F135">
+        <v>193.6639969244288</v>
+      </c>
+      <c r="G135">
+        <v>1281</v>
+      </c>
+      <c r="H135">
+        <v>4902</v>
+      </c>
+      <c r="I135">
+        <v>42</v>
+      </c>
+      <c r="J135">
+        <v>6183</v>
+      </c>
+    </row>
+    <row r="136" spans="1:10">
+      <c r="A136" t="s">
+        <v>11</v>
+      </c>
+      <c r="B136">
+        <v>128</v>
+      </c>
+      <c r="C136">
+        <v>0.0173789</v>
+      </c>
+      <c r="D136" t="s">
+        <v>20</v>
+      </c>
+      <c r="E136">
+        <v>152</v>
+      </c>
+      <c r="F136">
+        <v>193.6639969244288</v>
+      </c>
+      <c r="G136">
+        <v>1001</v>
+      </c>
+      <c r="H136">
+        <v>2506</v>
+      </c>
+      <c r="I136">
+        <v>4</v>
+      </c>
+      <c r="J136">
+        <v>3507</v>
+      </c>
+    </row>
+    <row r="137" spans="1:10">
+      <c r="A137" t="s">
+        <v>12</v>
+      </c>
+      <c r="B137">
+        <v>128</v>
+      </c>
+      <c r="C137">
+        <v>0.09822610000000001</v>
+      </c>
+      <c r="D137" t="s">
+        <v>20</v>
+      </c>
+      <c r="E137">
+        <v>161</v>
+      </c>
+      <c r="F137">
+        <v>202.2497833620557</v>
+      </c>
+      <c r="G137">
+        <v>614</v>
+      </c>
+      <c r="H137">
+        <v>1176</v>
+      </c>
+      <c r="I137">
+        <v>10</v>
+      </c>
+      <c r="J137">
+        <v>1790</v>
+      </c>
+    </row>
+    <row r="138" spans="1:10">
+      <c r="A138" t="s">
+        <v>13</v>
+      </c>
+      <c r="B138">
+        <v>128</v>
+      </c>
+      <c r="C138">
+        <v>0.1622748</v>
+      </c>
+      <c r="D138" t="s">
+        <v>20</v>
+      </c>
+      <c r="E138">
+        <v>152</v>
+      </c>
+      <c r="F138">
+        <v>193.6639969244288</v>
+      </c>
+      <c r="G138">
+        <v>790</v>
+      </c>
+      <c r="H138">
+        <v>2816</v>
+      </c>
+      <c r="I138">
+        <v>4</v>
+      </c>
+      <c r="J138">
+        <v>3606</v>
+      </c>
+    </row>
+    <row r="139" spans="1:10">
+      <c r="A139" t="s">
+        <v>14</v>
+      </c>
+      <c r="B139">
+        <v>128</v>
+      </c>
+      <c r="C139">
+        <v>0.03305300000000001</v>
+      </c>
+      <c r="D139" t="s">
+        <v>20</v>
+      </c>
+      <c r="E139">
+        <v>12</v>
+      </c>
+      <c r="F139">
+        <v>193.6639969244288</v>
+      </c>
+      <c r="G139">
+        <v>12</v>
+      </c>
+      <c r="H139">
+        <v>29</v>
+      </c>
+      <c r="I139">
+        <v>3</v>
+      </c>
+      <c r="J139">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="140" spans="1:10">
+      <c r="A140" t="s">
+        <v>15</v>
+      </c>
+      <c r="B140">
+        <v>128</v>
+      </c>
+      <c r="C140">
+        <v>0.3422766</v>
+      </c>
+      <c r="D140" t="s">
+        <v>20</v>
+      </c>
+      <c r="E140">
+        <v>4</v>
+      </c>
+      <c r="F140">
         <v>187.5929117988749</v>
       </c>
-      <c r="G101">
+      <c r="G140">
         <v>1281</v>
       </c>
-      <c r="H101">
+      <c r="H140">
         <v>4902</v>
       </c>
-      <c r="I101">
+      <c r="I140">
         <v>2</v>
       </c>
-      <c r="J101">
+      <c r="J140">
         <v>6183</v>
+      </c>
+    </row>
+    <row r="141" spans="1:10">
+      <c r="A141" t="s">
+        <v>16</v>
+      </c>
+      <c r="B141">
+        <v>128</v>
+      </c>
+      <c r="C141">
+        <v>0.3391801</v>
+      </c>
+      <c r="D141" t="s">
+        <v>20</v>
+      </c>
+      <c r="E141">
+        <v>152</v>
+      </c>
+      <c r="F141">
+        <v>193.6639969244288</v>
+      </c>
+      <c r="G141">
+        <v>1042</v>
+      </c>
+      <c r="H141">
+        <v>5069</v>
+      </c>
+      <c r="I141">
+        <v>22</v>
+      </c>
+      <c r="J141">
+        <v>6111</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/Vertical/hasil_gabungan_semua_sheet.xlsx
+++ b/Excel/Vertical/hasil_gabungan_semua_sheet.xlsx
@@ -477,7 +477,7 @@
         <v>16</v>
       </c>
       <c r="C2">
-        <v>0.0004822</v>
+        <v>0.0005032000000000001</v>
       </c>
       <c r="D2" t="s">
         <v>3</v>
@@ -509,7 +509,7 @@
         <v>16</v>
       </c>
       <c r="C3">
-        <v>0.0002534999999999999</v>
+        <v>0.0002433</v>
       </c>
       <c r="D3" t="s">
         <v>3</v>
@@ -541,7 +541,7 @@
         <v>16</v>
       </c>
       <c r="C4">
-        <v>0.0004101</v>
+        <v>0.0001963</v>
       </c>
       <c r="D4" t="s">
         <v>3</v>
@@ -573,7 +573,7 @@
         <v>16</v>
       </c>
       <c r="C5">
-        <v>0.0003179</v>
+        <v>0.0003287</v>
       </c>
       <c r="D5" t="s">
         <v>3</v>
@@ -605,7 +605,7 @@
         <v>16</v>
       </c>
       <c r="C6">
-        <v>0.0003319</v>
+        <v>0.0003375</v>
       </c>
       <c r="D6" t="s">
         <v>3</v>
@@ -637,16 +637,16 @@
         <v>16</v>
       </c>
       <c r="C7">
-        <v>0.0005113</v>
+        <v>0.0004804</v>
       </c>
       <c r="D7" t="s">
         <v>3</v>
       </c>
       <c r="E7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F7">
-        <v>23.09901951359279</v>
+        <v>23.12310562561766</v>
       </c>
       <c r="G7">
         <v>30</v>
@@ -655,7 +655,7 @@
         <v>58</v>
       </c>
       <c r="I7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J7">
         <v>88</v>
@@ -669,7 +669,7 @@
         <v>16</v>
       </c>
       <c r="C8">
-        <v>0.0005372</v>
+        <v>0.0005020000000000001</v>
       </c>
       <c r="D8" t="s">
         <v>3</v>
@@ -681,16 +681,16 @@
         <v>24.14213562373095</v>
       </c>
       <c r="G8">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="H8">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I8">
         <v>9</v>
       </c>
       <c r="J8">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -701,7 +701,7 @@
         <v>32</v>
       </c>
       <c r="C9">
-        <v>0.0034743</v>
+        <v>0.003523399999999999</v>
       </c>
       <c r="D9" t="s">
         <v>3</v>
@@ -733,7 +733,7 @@
         <v>32</v>
       </c>
       <c r="C10">
-        <v>0.0011258</v>
+        <v>0.0011045</v>
       </c>
       <c r="D10" t="s">
         <v>3</v>
@@ -765,7 +765,7 @@
         <v>32</v>
       </c>
       <c r="C11">
-        <v>0.0013158</v>
+        <v>0.0006369999999999999</v>
       </c>
       <c r="D11" t="s">
         <v>3</v>
@@ -780,13 +780,13 @@
         <v>103</v>
       </c>
       <c r="H11">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="I11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J11">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -797,7 +797,7 @@
         <v>32</v>
       </c>
       <c r="C12">
-        <v>0.0018366</v>
+        <v>0.0018679</v>
       </c>
       <c r="D12" t="s">
         <v>3</v>
@@ -829,7 +829,7 @@
         <v>32</v>
       </c>
       <c r="C13">
-        <v>0.0010794</v>
+        <v>0.0011568</v>
       </c>
       <c r="D13" t="s">
         <v>3</v>
@@ -861,16 +861,16 @@
         <v>32</v>
       </c>
       <c r="C14">
-        <v>0.0035126</v>
+        <v>0.0034676</v>
       </c>
       <c r="D14" t="s">
         <v>3</v>
       </c>
       <c r="E14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F14">
-        <v>46.86645192953345</v>
+        <v>47.00870142385959</v>
       </c>
       <c r="G14">
         <v>76</v>
@@ -879,7 +879,7 @@
         <v>241</v>
       </c>
       <c r="I14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J14">
         <v>317</v>
@@ -893,7 +893,7 @@
         <v>32</v>
       </c>
       <c r="C15">
-        <v>0.003432800000000001</v>
+        <v>0.0033985</v>
       </c>
       <c r="D15" t="s">
         <v>3</v>
@@ -905,7 +905,7 @@
         <v>49.698484809835</v>
       </c>
       <c r="G15">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="H15">
         <v>250</v>
@@ -914,7 +914,7 @@
         <v>10</v>
       </c>
       <c r="J15">
-        <v>316</v>
+        <v>320</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -925,7 +925,7 @@
         <v>64</v>
       </c>
       <c r="C16">
-        <v>0.025808</v>
+        <v>0.0245314</v>
       </c>
       <c r="D16" t="s">
         <v>3</v>
@@ -957,7 +957,7 @@
         <v>64</v>
       </c>
       <c r="C17">
-        <v>0.004922699999999999</v>
+        <v>0.004874399999999999</v>
       </c>
       <c r="D17" t="s">
         <v>3</v>
@@ -989,7 +989,7 @@
         <v>64</v>
       </c>
       <c r="C18">
-        <v>0.005923699999999999</v>
+        <v>0.0020404</v>
       </c>
       <c r="D18" t="s">
         <v>3</v>
@@ -998,19 +998,19 @@
         <v>84</v>
       </c>
       <c r="F18">
-        <v>103.2964645562817</v>
+        <v>102.4680374315355</v>
       </c>
       <c r="G18">
-        <v>264</v>
+        <v>219</v>
       </c>
       <c r="H18">
-        <v>142</v>
+        <v>88</v>
       </c>
       <c r="I18">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="J18">
-        <v>406</v>
+        <v>307</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -1021,7 +1021,7 @@
         <v>64</v>
       </c>
       <c r="C19">
-        <v>0.0129962</v>
+        <v>0.0127819</v>
       </c>
       <c r="D19" t="s">
         <v>3</v>
@@ -1053,7 +1053,7 @@
         <v>64</v>
       </c>
       <c r="C20">
-        <v>0.0036981</v>
+        <v>0.0036926</v>
       </c>
       <c r="D20" t="s">
         <v>3</v>
@@ -1085,7 +1085,7 @@
         <v>64</v>
       </c>
       <c r="C21">
-        <v>0.0248513</v>
+        <v>0.0243821</v>
       </c>
       <c r="D21" t="s">
         <v>3</v>
@@ -1094,7 +1094,7 @@
         <v>7</v>
       </c>
       <c r="F21">
-        <v>95.40233038888984</v>
+        <v>95.48180327461259</v>
       </c>
       <c r="G21">
         <v>166</v>
@@ -1117,7 +1117,7 @@
         <v>64</v>
       </c>
       <c r="C22">
-        <v>0.0224448</v>
+        <v>0.0220048</v>
       </c>
       <c r="D22" t="s">
         <v>3</v>
@@ -1129,7 +1129,7 @@
         <v>100.8111831820431</v>
       </c>
       <c r="G22">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="H22">
         <v>1005</v>
@@ -1138,7 +1138,7 @@
         <v>12</v>
       </c>
       <c r="J22">
-        <v>1164</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -1149,7 +1149,7 @@
         <v>128</v>
       </c>
       <c r="C23">
-        <v>0.15967</v>
+        <v>0.1620138</v>
       </c>
       <c r="D23" t="s">
         <v>3</v>
@@ -1181,7 +1181,7 @@
         <v>128</v>
       </c>
       <c r="C24">
-        <v>0.0205536</v>
+        <v>0.0203735</v>
       </c>
       <c r="D24" t="s">
         <v>3</v>
@@ -1213,7 +1213,7 @@
         <v>128</v>
       </c>
       <c r="C25">
-        <v>0.0429991</v>
+        <v>0.0074792</v>
       </c>
       <c r="D25" t="s">
         <v>3</v>
@@ -1222,19 +1222,19 @@
         <v>168</v>
       </c>
       <c r="F25">
-        <v>208.0071426749365</v>
+        <v>206.350288425444</v>
       </c>
       <c r="G25">
-        <v>643</v>
+        <v>460</v>
       </c>
       <c r="H25">
-        <v>587</v>
+        <v>196</v>
       </c>
       <c r="I25">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="J25">
-        <v>1230</v>
+        <v>656</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -1245,7 +1245,7 @@
         <v>128</v>
       </c>
       <c r="C26">
-        <v>0.08562030000000001</v>
+        <v>0.08665039999999999</v>
       </c>
       <c r="D26" t="s">
         <v>3</v>
@@ -1277,7 +1277,7 @@
         <v>128</v>
       </c>
       <c r="C27">
-        <v>0.0150779</v>
+        <v>0.015071</v>
       </c>
       <c r="D27" t="s">
         <v>3</v>
@@ -1309,7 +1309,7 @@
         <v>128</v>
       </c>
       <c r="C28">
-        <v>0.1598635</v>
+        <v>0.1615691</v>
       </c>
       <c r="D28" t="s">
         <v>3</v>
@@ -1341,7 +1341,7 @@
         <v>128</v>
       </c>
       <c r="C29">
-        <v>0.1517371</v>
+        <v>0.1549465</v>
       </c>
       <c r="D29" t="s">
         <v>3</v>
@@ -1353,7 +1353,7 @@
         <v>203.0365799264593</v>
       </c>
       <c r="G29">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="H29">
         <v>4034</v>
@@ -1362,7 +1362,7 @@
         <v>20</v>
       </c>
       <c r="J29">
-        <v>4407</v>
+        <v>4421</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -1373,7 +1373,7 @@
         <v>16</v>
       </c>
       <c r="C30">
-        <v>0.0005046</v>
+        <v>0.0004917</v>
       </c>
       <c r="D30" t="s">
         <v>17</v>
@@ -1405,7 +1405,7 @@
         <v>16</v>
       </c>
       <c r="C31">
-        <v>0.0003077</v>
+        <v>0.0002944000000000001</v>
       </c>
       <c r="D31" t="s">
         <v>17</v>
@@ -1437,28 +1437,28 @@
         <v>16</v>
       </c>
       <c r="C32">
-        <v>0.00055</v>
+        <v>0.0002705</v>
       </c>
       <c r="D32" t="s">
         <v>17</v>
       </c>
       <c r="E32">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F32">
-        <v>28.38477631085023</v>
+        <v>25.55634918610405</v>
       </c>
       <c r="G32">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="H32">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I32">
         <v>11</v>
       </c>
       <c r="J32">
-        <v>72</v>
+        <v>63</v>
       </c>
     </row>
     <row r="33" spans="1:10">
@@ -1469,7 +1469,7 @@
         <v>16</v>
       </c>
       <c r="C33">
-        <v>0.0004154</v>
+        <v>0.0004196</v>
       </c>
       <c r="D33" t="s">
         <v>17</v>
@@ -1501,7 +1501,7 @@
         <v>16</v>
       </c>
       <c r="C34">
-        <v>0.0003521</v>
+        <v>0.0004123</v>
       </c>
       <c r="D34" t="s">
         <v>17</v>
@@ -1533,7 +1533,7 @@
         <v>16</v>
       </c>
       <c r="C35">
-        <v>0.0006652</v>
+        <v>0.0004839999999999999</v>
       </c>
       <c r="D35" t="s">
         <v>17</v>
@@ -1542,7 +1542,7 @@
         <v>7</v>
       </c>
       <c r="F35">
-        <v>24.2748964148517</v>
+        <v>24.370154202675</v>
       </c>
       <c r="G35">
         <v>25</v>
@@ -1565,7 +1565,7 @@
         <v>16</v>
       </c>
       <c r="C36">
-        <v>0.0007118000000000001</v>
+        <v>0.0005338</v>
       </c>
       <c r="D36" t="s">
         <v>17</v>
@@ -1577,7 +1577,7 @@
         <v>25.55634918610405</v>
       </c>
       <c r="G36">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="H36">
         <v>69</v>
@@ -1586,7 +1586,7 @@
         <v>12</v>
       </c>
       <c r="J36">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="37" spans="1:10">
@@ -1597,7 +1597,7 @@
         <v>32</v>
       </c>
       <c r="C37">
-        <v>0.0029849</v>
+        <v>0.0029884</v>
       </c>
       <c r="D37" t="s">
         <v>17</v>
@@ -1629,7 +1629,7 @@
         <v>32</v>
       </c>
       <c r="C38">
-        <v>0.0012901</v>
+        <v>0.00127</v>
       </c>
       <c r="D38" t="s">
         <v>17</v>
@@ -1661,7 +1661,7 @@
         <v>32</v>
       </c>
       <c r="C39">
-        <v>0.0019769</v>
+        <v>0.0009784999999999998</v>
       </c>
       <c r="D39" t="s">
         <v>17</v>
@@ -1670,19 +1670,19 @@
         <v>44</v>
       </c>
       <c r="F39">
-        <v>52.52691193458119</v>
+        <v>51.69848480983499</v>
       </c>
       <c r="G39">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="H39">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I39">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J39">
-        <v>182</v>
+        <v>172</v>
       </c>
     </row>
     <row r="40" spans="1:10">
@@ -1693,7 +1693,7 @@
         <v>32</v>
       </c>
       <c r="C40">
-        <v>0.002414</v>
+        <v>0.002399</v>
       </c>
       <c r="D40" t="s">
         <v>17</v>
@@ -1725,7 +1725,7 @@
         <v>32</v>
       </c>
       <c r="C41">
-        <v>0.0010381</v>
+        <v>0.0010203</v>
       </c>
       <c r="D41" t="s">
         <v>17</v>
@@ -1757,7 +1757,7 @@
         <v>32</v>
       </c>
       <c r="C42">
-        <v>0.0030295</v>
+        <v>0.0029943</v>
       </c>
       <c r="D42" t="s">
         <v>17</v>
@@ -1789,7 +1789,7 @@
         <v>32</v>
       </c>
       <c r="C43">
-        <v>0.0029012</v>
+        <v>0.0028261</v>
       </c>
       <c r="D43" t="s">
         <v>17</v>
@@ -1801,7 +1801,7 @@
         <v>51.69848480983499</v>
       </c>
       <c r="G43">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="H43">
         <v>266</v>
@@ -1810,7 +1810,7 @@
         <v>14</v>
       </c>
       <c r="J43">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="44" spans="1:10">
@@ -1821,7 +1821,7 @@
         <v>64</v>
       </c>
       <c r="C44">
-        <v>0.0196066</v>
+        <v>0.0202147</v>
       </c>
       <c r="D44" t="s">
         <v>17</v>
@@ -1853,7 +1853,7 @@
         <v>64</v>
       </c>
       <c r="C45">
-        <v>0.0051455</v>
+        <v>0.0050963</v>
       </c>
       <c r="D45" t="s">
         <v>17</v>
@@ -1885,7 +1885,7 @@
         <v>64</v>
       </c>
       <c r="C46">
-        <v>0.0173749</v>
+        <v>0.005393600000000001</v>
       </c>
       <c r="D46" t="s">
         <v>17</v>
@@ -1894,19 +1894,19 @@
         <v>88</v>
       </c>
       <c r="F46">
-        <v>107.2964645562817</v>
+        <v>104.8111831820431</v>
       </c>
       <c r="G46">
-        <v>331</v>
+        <v>252</v>
       </c>
       <c r="H46">
-        <v>395</v>
+        <v>229</v>
       </c>
       <c r="I46">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J46">
-        <v>726</v>
+        <v>481</v>
       </c>
     </row>
     <row r="47" spans="1:10">
@@ -1917,7 +1917,7 @@
         <v>64</v>
       </c>
       <c r="C47">
-        <v>0.0163651</v>
+        <v>0.0166019</v>
       </c>
       <c r="D47" t="s">
         <v>17</v>
@@ -1949,7 +1949,7 @@
         <v>64</v>
       </c>
       <c r="C48">
-        <v>0.0034979</v>
+        <v>0.0035396</v>
       </c>
       <c r="D48" t="s">
         <v>17</v>
@@ -1981,7 +1981,7 @@
         <v>64</v>
       </c>
       <c r="C49">
-        <v>0.0197748</v>
+        <v>0.0199947</v>
       </c>
       <c r="D49" t="s">
         <v>17</v>
@@ -2013,7 +2013,7 @@
         <v>64</v>
       </c>
       <c r="C50">
-        <v>0.0183939</v>
+        <v>0.0189401</v>
       </c>
       <c r="D50" t="s">
         <v>17</v>
@@ -2045,7 +2045,7 @@
         <v>128</v>
       </c>
       <c r="C51">
-        <v>0.1302875</v>
+        <v>0.1326106</v>
       </c>
       <c r="D51" t="s">
         <v>17</v>
@@ -2077,7 +2077,7 @@
         <v>128</v>
       </c>
       <c r="C52">
-        <v>0.0220098</v>
+        <v>0.0216924</v>
       </c>
       <c r="D52" t="s">
         <v>17</v>
@@ -2109,7 +2109,7 @@
         <v>128</v>
       </c>
       <c r="C53">
-        <v>0.1626759</v>
+        <v>0.0299984</v>
       </c>
       <c r="D53" t="s">
         <v>17</v>
@@ -2118,19 +2118,19 @@
         <v>176</v>
       </c>
       <c r="F53">
-        <v>214.350288425444</v>
+        <v>211.8650070512055</v>
       </c>
       <c r="G53">
-        <v>836</v>
+        <v>540</v>
       </c>
       <c r="H53">
-        <v>1847</v>
+        <v>735</v>
       </c>
       <c r="I53">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J53">
-        <v>2683</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="54" spans="1:10">
@@ -2141,7 +2141,7 @@
         <v>128</v>
       </c>
       <c r="C54">
-        <v>0.1147033</v>
+        <v>0.1168257</v>
       </c>
       <c r="D54" t="s">
         <v>17</v>
@@ -2173,7 +2173,7 @@
         <v>128</v>
       </c>
       <c r="C55">
-        <v>0.0127862</v>
+        <v>0.0133145</v>
       </c>
       <c r="D55" t="s">
         <v>17</v>
@@ -2205,7 +2205,7 @@
         <v>128</v>
       </c>
       <c r="C56">
-        <v>0.1311289</v>
+        <v>0.1322051</v>
       </c>
       <c r="D56" t="s">
         <v>17</v>
@@ -2237,7 +2237,7 @@
         <v>128</v>
       </c>
       <c r="C57">
-        <v>0.1253862</v>
+        <v>0.1285134</v>
       </c>
       <c r="D57" t="s">
         <v>17</v>
@@ -2249,7 +2249,7 @@
         <v>208.5512985522207</v>
       </c>
       <c r="G57">
-        <v>322</v>
+        <v>336</v>
       </c>
       <c r="H57">
         <v>4201</v>
@@ -2258,7 +2258,7 @@
         <v>24</v>
       </c>
       <c r="J57">
-        <v>4523</v>
+        <v>4537</v>
       </c>
     </row>
     <row r="58" spans="1:10">
@@ -2269,7 +2269,7 @@
         <v>16</v>
       </c>
       <c r="C58">
-        <v>0.000411</v>
+        <v>0.0003857</v>
       </c>
       <c r="D58" t="s">
         <v>18</v>
@@ -2301,7 +2301,7 @@
         <v>16</v>
       </c>
       <c r="C59">
-        <v>0.000229</v>
+        <v>0.0002344</v>
       </c>
       <c r="D59" t="s">
         <v>18</v>
@@ -2333,28 +2333,28 @@
         <v>16</v>
       </c>
       <c r="C60">
-        <v>0.0003135</v>
+        <v>0.0001989</v>
       </c>
       <c r="D60" t="s">
         <v>18</v>
       </c>
       <c r="E60">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F60">
-        <v>26.72792206135786</v>
+        <v>25.31370849898476</v>
       </c>
       <c r="G60">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H60">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I60">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J60">
-        <v>44</v>
+        <v>51</v>
       </c>
     </row>
     <row r="61" spans="1:10">
@@ -2365,7 +2365,7 @@
         <v>16</v>
       </c>
       <c r="C61">
-        <v>0.0003295</v>
+        <v>0.0003264</v>
       </c>
       <c r="D61" t="s">
         <v>18</v>
@@ -2397,7 +2397,7 @@
         <v>16</v>
       </c>
       <c r="C62">
-        <v>0.0004089</v>
+        <v>0.0004107000000000001</v>
       </c>
       <c r="D62" t="s">
         <v>18</v>
@@ -2429,16 +2429,16 @@
         <v>16</v>
       </c>
       <c r="C63">
-        <v>0.0004338</v>
+        <v>0.0003958</v>
       </c>
       <c r="D63" t="s">
         <v>18</v>
       </c>
       <c r="E63">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F63">
-        <v>24.32285268768197</v>
+        <v>24.54572853696417</v>
       </c>
       <c r="G63">
         <v>13</v>
@@ -2447,7 +2447,7 @@
         <v>59</v>
       </c>
       <c r="I63">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J63">
         <v>72</v>
@@ -2461,7 +2461,7 @@
         <v>16</v>
       </c>
       <c r="C64">
-        <v>0.0004282</v>
+        <v>0.0004186</v>
       </c>
       <c r="D64" t="s">
         <v>18</v>
@@ -2473,7 +2473,7 @@
         <v>25.31370849898476</v>
       </c>
       <c r="G64">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H64">
         <v>62</v>
@@ -2482,7 +2482,7 @@
         <v>13</v>
       </c>
       <c r="J64">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="65" spans="1:10">
@@ -2493,7 +2493,7 @@
         <v>32</v>
       </c>
       <c r="C65">
-        <v>0.0025615</v>
+        <v>0.0025202</v>
       </c>
       <c r="D65" t="s">
         <v>18</v>
@@ -2525,7 +2525,7 @@
         <v>32</v>
       </c>
       <c r="C66">
-        <v>0.0010567</v>
+        <v>0.0010261</v>
       </c>
       <c r="D66" t="s">
         <v>18</v>
@@ -2557,7 +2557,7 @@
         <v>32</v>
       </c>
       <c r="C67">
-        <v>0.0014422</v>
+        <v>0.0007438999999999999</v>
       </c>
       <c r="D67" t="s">
         <v>18</v>
@@ -2569,16 +2569,16 @@
         <v>54.04163056034262</v>
       </c>
       <c r="G67">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="H67">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I67">
         <v>16</v>
       </c>
       <c r="J67">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="68" spans="1:10">
@@ -2589,7 +2589,7 @@
         <v>32</v>
       </c>
       <c r="C68">
-        <v>0.0020269</v>
+        <v>0.0019956</v>
       </c>
       <c r="D68" t="s">
         <v>18</v>
@@ -2621,7 +2621,7 @@
         <v>32</v>
       </c>
       <c r="C69">
-        <v>0.0013142</v>
+        <v>0.0013024</v>
       </c>
       <c r="D69" t="s">
         <v>18</v>
@@ -2653,7 +2653,7 @@
         <v>32</v>
       </c>
       <c r="C70">
-        <v>0.002598899999999999</v>
+        <v>0.0025725</v>
       </c>
       <c r="D70" t="s">
         <v>18</v>
@@ -2685,7 +2685,7 @@
         <v>32</v>
       </c>
       <c r="C71">
-        <v>0.0024118</v>
+        <v>0.0023666</v>
       </c>
       <c r="D71" t="s">
         <v>18</v>
@@ -2697,7 +2697,7 @@
         <v>52.04163056034262</v>
       </c>
       <c r="G71">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H71">
         <v>248</v>
@@ -2706,7 +2706,7 @@
         <v>12</v>
       </c>
       <c r="J71">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="72" spans="1:10">
@@ -2717,7 +2717,7 @@
         <v>64</v>
       </c>
       <c r="C72">
-        <v>0.0168613</v>
+        <v>0.0171838</v>
       </c>
       <c r="D72" t="s">
         <v>18</v>
@@ -2749,7 +2749,7 @@
         <v>64</v>
       </c>
       <c r="C73">
-        <v>0.004311999999999999</v>
+        <v>0.0043424</v>
       </c>
       <c r="D73" t="s">
         <v>18</v>
@@ -2781,28 +2781,28 @@
         <v>64</v>
       </c>
       <c r="C74">
-        <v>0.0093718</v>
+        <v>0.002988</v>
       </c>
       <c r="D74" t="s">
         <v>18</v>
       </c>
       <c r="E74">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="F74">
-        <v>106.3259018078045</v>
+        <v>108.6690475583121</v>
       </c>
       <c r="G74">
-        <v>229</v>
+        <v>174</v>
       </c>
       <c r="H74">
-        <v>267</v>
+        <v>144</v>
       </c>
       <c r="I74">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J74">
-        <v>496</v>
+        <v>318</v>
       </c>
     </row>
     <row r="75" spans="1:10">
@@ -2813,7 +2813,7 @@
         <v>64</v>
       </c>
       <c r="C75">
-        <v>0.0135943</v>
+        <v>0.0142777</v>
       </c>
       <c r="D75" t="s">
         <v>18</v>
@@ -2845,7 +2845,7 @@
         <v>64</v>
       </c>
       <c r="C76">
-        <v>0.004973300000000001</v>
+        <v>0.004972600000000001</v>
       </c>
       <c r="D76" t="s">
         <v>18</v>
@@ -2877,7 +2877,7 @@
         <v>64</v>
       </c>
       <c r="C77">
-        <v>0.0171851</v>
+        <v>0.0173022</v>
       </c>
       <c r="D77" t="s">
         <v>18</v>
@@ -2909,7 +2909,7 @@
         <v>64</v>
       </c>
       <c r="C78">
-        <v>0.0149212</v>
+        <v>0.0151008</v>
       </c>
       <c r="D78" t="s">
         <v>18</v>
@@ -2921,7 +2921,7 @@
         <v>105.4974746830583</v>
       </c>
       <c r="G78">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="H78">
         <v>995</v>
@@ -2930,7 +2930,7 @@
         <v>18</v>
       </c>
       <c r="J78">
-        <v>1099</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="79" spans="1:10">
@@ -2941,7 +2941,7 @@
         <v>128</v>
       </c>
       <c r="C79">
-        <v>0.1104541</v>
+        <v>0.1113246</v>
       </c>
       <c r="D79" t="s">
         <v>18</v>
@@ -2973,7 +2973,7 @@
         <v>128</v>
       </c>
       <c r="C80">
-        <v>0.0179439</v>
+        <v>0.0178264</v>
       </c>
       <c r="D80" t="s">
         <v>18</v>
@@ -3005,28 +3005,28 @@
         <v>128</v>
       </c>
       <c r="C81">
-        <v>0.07056939999999999</v>
+        <v>0.0138025</v>
       </c>
       <c r="D81" t="s">
         <v>18</v>
       </c>
       <c r="E81">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="F81">
-        <v>214.0660171779821</v>
+        <v>218.7523086789974</v>
       </c>
       <c r="G81">
-        <v>544</v>
+        <v>417</v>
       </c>
       <c r="H81">
-        <v>1070</v>
+        <v>394</v>
       </c>
       <c r="I81">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="J81">
-        <v>1614</v>
+        <v>811</v>
       </c>
     </row>
     <row r="82" spans="1:10">
@@ -3037,7 +3037,7 @@
         <v>128</v>
       </c>
       <c r="C82">
-        <v>0.08971359999999999</v>
+        <v>0.09037300000000001</v>
       </c>
       <c r="D82" t="s">
         <v>18</v>
@@ -3069,7 +3069,7 @@
         <v>128</v>
       </c>
       <c r="C83">
-        <v>0.0216076</v>
+        <v>0.0217999</v>
       </c>
       <c r="D83" t="s">
         <v>18</v>
@@ -3101,7 +3101,7 @@
         <v>128</v>
       </c>
       <c r="C84">
-        <v>0.1110167</v>
+        <v>0.1117027</v>
       </c>
       <c r="D84" t="s">
         <v>18</v>
@@ -3133,7 +3133,7 @@
         <v>128</v>
       </c>
       <c r="C85">
-        <v>0.0993503</v>
+        <v>0.1007172</v>
       </c>
       <c r="D85" t="s">
         <v>18</v>
@@ -3145,7 +3145,7 @@
         <v>212.4091629284898</v>
       </c>
       <c r="G85">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H85">
         <v>3952</v>
@@ -3154,7 +3154,7 @@
         <v>20</v>
       </c>
       <c r="J85">
-        <v>4199</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="86" spans="1:10">
@@ -3165,7 +3165,7 @@
         <v>16</v>
       </c>
       <c r="C86">
-        <v>0.0006736</v>
+        <v>0.0005730000000000001</v>
       </c>
       <c r="D86" t="s">
         <v>19</v>
@@ -3197,7 +3197,7 @@
         <v>16</v>
       </c>
       <c r="C87">
-        <v>0.00026</v>
+        <v>0.0002544</v>
       </c>
       <c r="D87" t="s">
         <v>19</v>
@@ -3229,7 +3229,7 @@
         <v>16</v>
       </c>
       <c r="C88">
-        <v>0.0003932000000000001</v>
+        <v>0.000196</v>
       </c>
       <c r="D88" t="s">
         <v>19</v>
@@ -3261,7 +3261,7 @@
         <v>16</v>
       </c>
       <c r="C89">
-        <v>0.000454</v>
+        <v>0.0004541000000000001</v>
       </c>
       <c r="D89" t="s">
         <v>19</v>
@@ -3293,7 +3293,7 @@
         <v>16</v>
       </c>
       <c r="C90">
-        <v>0.0004305</v>
+        <v>0.0004201</v>
       </c>
       <c r="D90" t="s">
         <v>19</v>
@@ -3325,7 +3325,7 @@
         <v>16</v>
       </c>
       <c r="C91">
-        <v>0.0007059999999999999</v>
+        <v>0.0005912000000000001</v>
       </c>
       <c r="D91" t="s">
         <v>19</v>
@@ -3334,7 +3334,7 @@
         <v>6</v>
       </c>
       <c r="F91">
-        <v>22.56073125075471</v>
+        <v>22.73887683562801</v>
       </c>
       <c r="G91">
         <v>34</v>
@@ -3357,7 +3357,7 @@
         <v>16</v>
       </c>
       <c r="C92">
-        <v>0.0006441000000000001</v>
+        <v>0.0005688000000000001</v>
       </c>
       <c r="D92" t="s">
         <v>19</v>
@@ -3369,10 +3369,10 @@
         <v>23.55634918610405</v>
       </c>
       <c r="G92">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H92">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="I92">
         <v>11</v>
@@ -3389,7 +3389,7 @@
         <v>32</v>
       </c>
       <c r="C93">
-        <v>0.003875100000000001</v>
+        <v>0.0039611</v>
       </c>
       <c r="D93" t="s">
         <v>19</v>
@@ -3421,7 +3421,7 @@
         <v>32</v>
       </c>
       <c r="C94">
-        <v>0.0011789</v>
+        <v>0.0011466</v>
       </c>
       <c r="D94" t="s">
         <v>19</v>
@@ -3453,7 +3453,7 @@
         <v>32</v>
       </c>
       <c r="C95">
-        <v>0.0014195</v>
+        <v>0.0006352</v>
       </c>
       <c r="D95" t="s">
         <v>19</v>
@@ -3462,19 +3462,19 @@
         <v>40</v>
       </c>
       <c r="F95">
-        <v>50.18376618407358</v>
+        <v>49.35533905932738</v>
       </c>
       <c r="G95">
         <v>91</v>
       </c>
       <c r="H95">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="I95">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="J95">
-        <v>152</v>
+        <v>140</v>
       </c>
     </row>
     <row r="96" spans="1:10">
@@ -3485,7 +3485,7 @@
         <v>32</v>
       </c>
       <c r="C96">
-        <v>0.002692</v>
+        <v>0.0026946</v>
       </c>
       <c r="D96" t="s">
         <v>19</v>
@@ -3517,7 +3517,7 @@
         <v>32</v>
       </c>
       <c r="C97">
-        <v>0.0013392</v>
+        <v>0.0013573</v>
       </c>
       <c r="D97" t="s">
         <v>19</v>
@@ -3549,7 +3549,7 @@
         <v>32</v>
       </c>
       <c r="C98">
-        <v>0.0039451</v>
+        <v>0.0038404</v>
       </c>
       <c r="D98" t="s">
         <v>19</v>
@@ -3581,7 +3581,7 @@
         <v>32</v>
       </c>
       <c r="C99">
-        <v>0.0044204</v>
+        <v>0.0037471</v>
       </c>
       <c r="D99" t="s">
         <v>19</v>
@@ -3593,7 +3593,7 @@
         <v>48.52691193458118</v>
       </c>
       <c r="G99">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="H99">
         <v>289</v>
@@ -3602,7 +3602,7 @@
         <v>12</v>
       </c>
       <c r="J99">
-        <v>377</v>
+        <v>382</v>
       </c>
     </row>
     <row r="100" spans="1:10">
@@ -3613,7 +3613,7 @@
         <v>64</v>
       </c>
       <c r="C100">
-        <v>0.0296328</v>
+        <v>0.0298233</v>
       </c>
       <c r="D100" t="s">
         <v>19</v>
@@ -3645,7 +3645,7 @@
         <v>64</v>
       </c>
       <c r="C101">
-        <v>0.0051299</v>
+        <v>0.0050745</v>
       </c>
       <c r="D101" t="s">
         <v>19</v>
@@ -3677,28 +3677,28 @@
         <v>64</v>
       </c>
       <c r="C102">
-        <v>0.0058033</v>
+        <v>0.0026319</v>
       </c>
       <c r="D102" t="s">
         <v>19</v>
       </c>
       <c r="E102">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F102">
-        <v>102.3675323681472</v>
+        <v>100.953318805774</v>
       </c>
       <c r="G102">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="H102">
-        <v>160</v>
+        <v>115</v>
       </c>
       <c r="I102">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J102">
-        <v>390</v>
+        <v>331</v>
       </c>
     </row>
     <row r="103" spans="1:10">
@@ -3709,7 +3709,7 @@
         <v>64</v>
       </c>
       <c r="C103">
-        <v>0.0183267</v>
+        <v>0.0186878</v>
       </c>
       <c r="D103" t="s">
         <v>19</v>
@@ -3741,7 +3741,7 @@
         <v>64</v>
       </c>
       <c r="C104">
-        <v>0.0050223</v>
+        <v>0.0050461</v>
       </c>
       <c r="D104" t="s">
         <v>19</v>
@@ -3773,7 +3773,7 @@
         <v>64</v>
       </c>
       <c r="C105">
-        <v>0.029346</v>
+        <v>0.0296411</v>
       </c>
       <c r="D105" t="s">
         <v>19</v>
@@ -3805,7 +3805,7 @@
         <v>64</v>
       </c>
       <c r="C106">
-        <v>0.0279673</v>
+        <v>0.028635</v>
       </c>
       <c r="D106" t="s">
         <v>19</v>
@@ -3817,7 +3817,7 @@
         <v>98.46803743153546</v>
       </c>
       <c r="G106">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="H106">
         <v>1212</v>
@@ -3826,7 +3826,7 @@
         <v>12</v>
       </c>
       <c r="J106">
-        <v>1498</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="107" spans="1:10">
@@ -3837,7 +3837,7 @@
         <v>128</v>
       </c>
       <c r="C107">
-        <v>0.2242598</v>
+        <v>0.2253527</v>
       </c>
       <c r="D107" t="s">
         <v>19</v>
@@ -3869,7 +3869,7 @@
         <v>128</v>
       </c>
       <c r="C108">
-        <v>0.022055</v>
+        <v>0.0216949</v>
       </c>
       <c r="D108" t="s">
         <v>19</v>
@@ -3901,28 +3901,28 @@
         <v>128</v>
       </c>
       <c r="C109">
-        <v>0.0368362</v>
+        <v>0.0129174</v>
       </c>
       <c r="D109" t="s">
         <v>19</v>
       </c>
       <c r="E109">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F109">
-        <v>204.7350647362943</v>
+        <v>203.3208511739212</v>
       </c>
       <c r="G109">
-        <v>625</v>
+        <v>488</v>
       </c>
       <c r="H109">
-        <v>581</v>
+        <v>316</v>
       </c>
       <c r="I109">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="J109">
-        <v>1206</v>
+        <v>804</v>
       </c>
     </row>
     <row r="110" spans="1:10">
@@ -3933,7 +3933,7 @@
         <v>128</v>
       </c>
       <c r="C110">
-        <v>0.1254835</v>
+        <v>0.1292262</v>
       </c>
       <c r="D110" t="s">
         <v>19</v>
@@ -3965,7 +3965,7 @@
         <v>128</v>
       </c>
       <c r="C111">
-        <v>0.0206832</v>
+        <v>0.020667</v>
       </c>
       <c r="D111" t="s">
         <v>19</v>
@@ -3997,7 +3997,7 @@
         <v>128</v>
       </c>
       <c r="C112">
-        <v>0.2232106</v>
+        <v>0.2263918</v>
       </c>
       <c r="D112" t="s">
         <v>19</v>
@@ -4029,7 +4029,7 @@
         <v>128</v>
       </c>
       <c r="C113">
-        <v>0.2098544</v>
+        <v>0.2141135</v>
       </c>
       <c r="D113" t="s">
         <v>19</v>
@@ -4041,7 +4041,7 @@
         <v>198.350288425444</v>
       </c>
       <c r="G113">
-        <v>706</v>
+        <v>744</v>
       </c>
       <c r="H113">
         <v>4951</v>
@@ -4050,7 +4050,7 @@
         <v>18</v>
       </c>
       <c r="J113">
-        <v>5657</v>
+        <v>5695</v>
       </c>
     </row>
     <row r="114" spans="1:10">
@@ -4061,7 +4061,7 @@
         <v>16</v>
       </c>
       <c r="C114">
-        <v>0.0007793</v>
+        <v>0.0014131</v>
       </c>
       <c r="D114" t="s">
         <v>20</v>
@@ -4093,7 +4093,7 @@
         <v>16</v>
       </c>
       <c r="C115">
-        <v>0.00029</v>
+        <v>0.000253</v>
       </c>
       <c r="D115" t="s">
         <v>20</v>
@@ -4125,7 +4125,7 @@
         <v>16</v>
       </c>
       <c r="C116">
-        <v>0.0004352</v>
+        <v>0.0001992</v>
       </c>
       <c r="D116" t="s">
         <v>20</v>
@@ -4137,10 +4137,10 @@
         <v>24.38477631085024</v>
       </c>
       <c r="G116">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H116">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I116">
         <v>7</v>
@@ -4157,7 +4157,7 @@
         <v>16</v>
       </c>
       <c r="C117">
-        <v>0.0006098</v>
+        <v>0.0006092999999999999</v>
       </c>
       <c r="D117" t="s">
         <v>20</v>
@@ -4189,7 +4189,7 @@
         <v>16</v>
       </c>
       <c r="C118">
-        <v>0.0006093</v>
+        <v>0.0006078</v>
       </c>
       <c r="D118" t="s">
         <v>20</v>
@@ -4221,7 +4221,7 @@
         <v>16</v>
       </c>
       <c r="C119">
-        <v>0.0008636999999999999</v>
+        <v>0.0008003999999999999</v>
       </c>
       <c r="D119" t="s">
         <v>20</v>
@@ -4253,7 +4253,7 @@
         <v>16</v>
       </c>
       <c r="C120">
-        <v>0.0009927</v>
+        <v>0.0010103</v>
       </c>
       <c r="D120" t="s">
         <v>20</v>
@@ -4285,7 +4285,7 @@
         <v>32</v>
       </c>
       <c r="C121">
-        <v>0.0057743</v>
+        <v>0.005987899999999999</v>
       </c>
       <c r="D121" t="s">
         <v>20</v>
@@ -4317,7 +4317,7 @@
         <v>32</v>
       </c>
       <c r="C122">
-        <v>0.0009507</v>
+        <v>0.0009589000000000001</v>
       </c>
       <c r="D122" t="s">
         <v>20</v>
@@ -4349,7 +4349,7 @@
         <v>32</v>
       </c>
       <c r="C123">
-        <v>0.0015813</v>
+        <v>0.0005905999999999999</v>
       </c>
       <c r="D123" t="s">
         <v>20</v>
@@ -4361,16 +4361,16 @@
         <v>49.35533905932738</v>
       </c>
       <c r="G123">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="H123">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="I123">
         <v>8</v>
       </c>
       <c r="J123">
-        <v>162</v>
+        <v>142</v>
       </c>
     </row>
     <row r="124" spans="1:10">
@@ -4381,7 +4381,7 @@
         <v>32</v>
       </c>
       <c r="C124">
-        <v>0.0035952</v>
+        <v>0.003592799999999999</v>
       </c>
       <c r="D124" t="s">
         <v>20</v>
@@ -4413,7 +4413,7 @@
         <v>32</v>
       </c>
       <c r="C125">
-        <v>0.0021138</v>
+        <v>0.0021167</v>
       </c>
       <c r="D125" t="s">
         <v>20</v>
@@ -4445,7 +4445,7 @@
         <v>32</v>
       </c>
       <c r="C126">
-        <v>0.0058417</v>
+        <v>0.0058376</v>
       </c>
       <c r="D126" t="s">
         <v>20</v>
@@ -4477,7 +4477,7 @@
         <v>32</v>
       </c>
       <c r="C127">
-        <v>0.007036299999999998</v>
+        <v>0.0069051</v>
       </c>
       <c r="D127" t="s">
         <v>20</v>
@@ -4489,7 +4489,7 @@
         <v>47.35533905932738</v>
       </c>
       <c r="G127">
-        <v>214</v>
+        <v>230</v>
       </c>
       <c r="H127">
         <v>337</v>
@@ -4498,7 +4498,7 @@
         <v>8</v>
       </c>
       <c r="J127">
-        <v>551</v>
+        <v>567</v>
       </c>
     </row>
     <row r="128" spans="1:10">
@@ -4509,7 +4509,7 @@
         <v>64</v>
       </c>
       <c r="C128">
-        <v>0.0501117</v>
+        <v>0.0491155</v>
       </c>
       <c r="D128" t="s">
         <v>20</v>
@@ -4541,7 +4541,7 @@
         <v>64</v>
       </c>
       <c r="C129">
-        <v>0.0037831</v>
+        <v>0.003908</v>
       </c>
       <c r="D129" t="s">
         <v>20</v>
@@ -4573,7 +4573,7 @@
         <v>64</v>
       </c>
       <c r="C130">
-        <v>0.0118541</v>
+        <v>0.0020338</v>
       </c>
       <c r="D130" t="s">
         <v>20</v>
@@ -4585,16 +4585,16 @@
         <v>100.1248916810278</v>
       </c>
       <c r="G130">
-        <v>292</v>
+        <v>223</v>
       </c>
       <c r="H130">
-        <v>263</v>
+        <v>85</v>
       </c>
       <c r="I130">
         <v>8</v>
       </c>
       <c r="J130">
-        <v>555</v>
+        <v>308</v>
       </c>
     </row>
     <row r="131" spans="1:10">
@@ -4605,7 +4605,7 @@
         <v>64</v>
       </c>
       <c r="C131">
-        <v>0.023993</v>
+        <v>0.0239114</v>
       </c>
       <c r="D131" t="s">
         <v>20</v>
@@ -4637,7 +4637,7 @@
         <v>64</v>
       </c>
       <c r="C132">
-        <v>0.0080479</v>
+        <v>0.008017800000000002</v>
       </c>
       <c r="D132" t="s">
         <v>20</v>
@@ -4669,7 +4669,7 @@
         <v>64</v>
       </c>
       <c r="C133">
-        <v>0.0502154</v>
+        <v>0.0494466</v>
       </c>
       <c r="D133" t="s">
         <v>20</v>
@@ -4701,7 +4701,7 @@
         <v>64</v>
       </c>
       <c r="C134">
-        <v>0.0504695</v>
+        <v>0.0511769</v>
       </c>
       <c r="D134" t="s">
         <v>20</v>
@@ -4713,7 +4713,7 @@
         <v>96.12489168102785</v>
       </c>
       <c r="G134">
-        <v>503</v>
+        <v>526</v>
       </c>
       <c r="H134">
         <v>1301</v>
@@ -4722,7 +4722,7 @@
         <v>14</v>
       </c>
       <c r="J134">
-        <v>1804</v>
+        <v>1827</v>
       </c>
     </row>
     <row r="135" spans="1:10">
@@ -4733,7 +4733,7 @@
         <v>128</v>
       </c>
       <c r="C135">
-        <v>0.340181</v>
+        <v>0.3437210000000001</v>
       </c>
       <c r="D135" t="s">
         <v>20</v>
@@ -4765,7 +4765,7 @@
         <v>128</v>
       </c>
       <c r="C136">
-        <v>0.0173789</v>
+        <v>0.0157092</v>
       </c>
       <c r="D136" t="s">
         <v>20</v>
@@ -4797,28 +4797,28 @@
         <v>128</v>
       </c>
       <c r="C137">
-        <v>0.09822610000000001</v>
+        <v>0.0075347</v>
       </c>
       <c r="D137" t="s">
         <v>20</v>
       </c>
       <c r="E137">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F137">
-        <v>202.2497833620557</v>
+        <v>201.6639969244288</v>
       </c>
       <c r="G137">
-        <v>614</v>
+        <v>476</v>
       </c>
       <c r="H137">
-        <v>1176</v>
+        <v>188</v>
       </c>
       <c r="I137">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J137">
-        <v>1790</v>
+        <v>664</v>
       </c>
     </row>
     <row r="138" spans="1:10">
@@ -4829,7 +4829,7 @@
         <v>128</v>
       </c>
       <c r="C138">
-        <v>0.1622748</v>
+        <v>0.1644629</v>
       </c>
       <c r="D138" t="s">
         <v>20</v>
@@ -4861,7 +4861,7 @@
         <v>128</v>
       </c>
       <c r="C139">
-        <v>0.03305300000000001</v>
+        <v>0.0331036</v>
       </c>
       <c r="D139" t="s">
         <v>20</v>
@@ -4893,7 +4893,7 @@
         <v>128</v>
       </c>
       <c r="C140">
-        <v>0.3422766</v>
+        <v>0.3435911</v>
       </c>
       <c r="D140" t="s">
         <v>20</v>
@@ -4925,7 +4925,7 @@
         <v>128</v>
       </c>
       <c r="C141">
-        <v>0.3391801</v>
+        <v>0.3472421</v>
       </c>
       <c r="D141" t="s">
         <v>20</v>
@@ -4937,7 +4937,7 @@
         <v>193.6639969244288</v>
       </c>
       <c r="G141">
-        <v>1042</v>
+        <v>1079</v>
       </c>
       <c r="H141">
         <v>5069</v>
@@ -4946,7 +4946,7 @@
         <v>22</v>
       </c>
       <c r="J141">
-        <v>6111</v>
+        <v>6148</v>
       </c>
     </row>
   </sheetData>
